--- a/poker/resources/sample/RobotAction_Chess.xlsx
+++ b/poker/resources/sample/RobotAction_Chess.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="ChessRobot" sheetId="1" r:id="rId1"/>
@@ -150,7 +150,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="58">
   <si>
     <t>序列</t>
   </si>
@@ -521,6 +521,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -534,18 +546,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -996,6 +996,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1008,17 +1010,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1545,7 +1545,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N34"/>
+  <dimension ref="A1:N49"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="3" width="10.875" customWidth="1"/>
@@ -1584,19 +1584,19 @@
       <c r="I1" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="K1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="L1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="M1" s="10" t="s">
+      <c r="M1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="N1" s="10" t="s">
+      <c r="N1" s="3" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1607,18 +1607,18 @@
       <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="2"/>
+      <c r="C2" s="4"/>
       <c r="D2" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="2"/>
+      <c r="F2" s="4"/>
       <c r="G2" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="5" t="s">
         <v>13</v>
       </c>
       <c r="J2" t="s">
@@ -1641,15 +1641,15 @@
       <c r="A3" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2" t="s">
+      <c r="C3" s="4"/>
+      <c r="D3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
       <c r="G3" t="s">
         <v>18</v>
       </c>
@@ -1675,30 +1675,30 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" ht="16.5" spans="2:6">
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
+    <row r="4" ht="16.5" spans="1:14">
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
     </row>
     <row r="5" ht="16.5" spans="1:14">
       <c r="A5">
         <v>200001</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="6">
         <v>20099</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="7">
         <v>3001001</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="8" t="s">
         <v>28</v>
       </c>
       <c r="G5" t="s">
@@ -1730,19 +1730,19 @@
       <c r="A6">
         <v>200002</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6" s="6">
         <v>20099</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="7">
         <v>3001002</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G6" t="s">
@@ -1774,19 +1774,19 @@
       <c r="A7">
         <v>200003</v>
       </c>
-      <c r="B7" s="4">
+      <c r="B7" s="6">
         <v>20099</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="7">
         <v>3001003</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="F7" s="10" t="s">
         <v>35</v>
       </c>
       <c r="G7" t="s">
@@ -1818,19 +1818,19 @@
       <c r="A8">
         <v>200004</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8" s="6">
         <v>20075</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8" s="7">
         <v>3001001</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F8" s="8" t="s">
         <v>28</v>
       </c>
       <c r="G8" t="s">
@@ -1862,19 +1862,19 @@
       <c r="A9">
         <v>200005</v>
       </c>
-      <c r="B9" s="4">
+      <c r="B9" s="6">
         <v>20075</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D9" s="7">
         <v>3001002</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G9" t="s">
@@ -1906,19 +1906,19 @@
       <c r="A10">
         <v>200006</v>
       </c>
-      <c r="B10" s="4">
+      <c r="B10" s="6">
         <v>20075</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="5">
+      <c r="D10" s="7">
         <v>3001003</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="F10" s="10" t="s">
         <v>35</v>
       </c>
       <c r="G10" t="s">
@@ -1950,19 +1950,19 @@
       <c r="A11">
         <v>200007</v>
       </c>
-      <c r="B11" s="4">
+      <c r="B11" s="6">
         <v>20050</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="D11" s="5">
+      <c r="D11" s="7">
         <v>3001001</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="F11" s="6" t="s">
+      <c r="F11" s="8" t="s">
         <v>28</v>
       </c>
       <c r="G11" t="s">
@@ -1994,19 +1994,19 @@
       <c r="A12">
         <v>200008</v>
       </c>
-      <c r="B12" s="4">
+      <c r="B12" s="6">
         <v>20050</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="D12" s="5">
+      <c r="D12" s="7">
         <v>3001002</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E12" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G12" t="s">
@@ -2038,19 +2038,19 @@
       <c r="A13">
         <v>200009</v>
       </c>
-      <c r="B13" s="4">
+      <c r="B13" s="6">
         <v>20050</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="D13" s="5">
+      <c r="D13" s="7">
         <v>3001003</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="E13" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="F13" s="8" t="s">
+      <c r="F13" s="10" t="s">
         <v>35</v>
       </c>
       <c r="G13" t="s">
@@ -2082,19 +2082,19 @@
       <c r="A14">
         <v>200010</v>
       </c>
-      <c r="B14" s="4">
+      <c r="B14" s="6">
         <v>20025</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="D14" s="5">
+      <c r="D14" s="7">
         <v>3001001</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="F14" s="6" t="s">
+      <c r="F14" s="8" t="s">
         <v>28</v>
       </c>
       <c r="G14" t="s">
@@ -2126,19 +2126,19 @@
       <c r="A15">
         <v>200011</v>
       </c>
-      <c r="B15" s="4">
+      <c r="B15" s="6">
         <v>20025</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="D15" s="5">
+      <c r="D15" s="7">
         <v>3001002</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="E15" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="F15" s="7" t="s">
+      <c r="F15" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G15" t="s">
@@ -2170,19 +2170,19 @@
       <c r="A16">
         <v>200012</v>
       </c>
-      <c r="B16" s="4">
+      <c r="B16" s="6">
         <v>20025</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="D16" s="5">
+      <c r="D16" s="7">
         <v>3001003</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="E16" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="F16" s="8" t="s">
+      <c r="F16" s="10" t="s">
         <v>35</v>
       </c>
       <c r="G16" t="s">
@@ -2214,19 +2214,19 @@
       <c r="A17">
         <v>200013</v>
       </c>
-      <c r="B17" s="4">
+      <c r="B17" s="6">
         <v>20001</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="D17" s="5">
+      <c r="D17" s="7">
         <v>3001001</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="E17" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="F17" s="6" t="s">
+      <c r="F17" s="8" t="s">
         <v>28</v>
       </c>
       <c r="G17" t="s">
@@ -2258,19 +2258,19 @@
       <c r="A18">
         <v>200014</v>
       </c>
-      <c r="B18" s="4">
+      <c r="B18" s="6">
         <v>20001</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="D18" s="5">
+      <c r="D18" s="7">
         <v>3001002</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="E18" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="F18" s="7" t="s">
+      <c r="F18" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G18" t="s">
@@ -2302,19 +2302,19 @@
       <c r="A19">
         <v>200015</v>
       </c>
-      <c r="B19" s="4">
+      <c r="B19" s="6">
         <v>20001</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="D19" s="5">
+      <c r="D19" s="7">
         <v>3001003</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="E19" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="F19" s="8" t="s">
+      <c r="F19" s="10" t="s">
         <v>35</v>
       </c>
       <c r="G19" t="s">
@@ -2346,19 +2346,19 @@
       <c r="A20">
         <v>200016</v>
       </c>
-      <c r="B20" s="4">
+      <c r="B20" s="6">
         <v>20099</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D20" s="5">
+      <c r="D20" s="7">
         <v>3002001</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="E20" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="F20" s="6" t="s">
+      <c r="F20" s="8" t="s">
         <v>28</v>
       </c>
       <c r="G20" t="s">
@@ -2390,19 +2390,19 @@
       <c r="A21">
         <v>200017</v>
       </c>
-      <c r="B21" s="4">
+      <c r="B21" s="6">
         <v>20099</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D21" s="5">
+      <c r="D21" s="7">
         <v>3002002</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="E21" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="F21" s="7" t="s">
+      <c r="F21" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G21" t="s">
@@ -2434,19 +2434,19 @@
       <c r="A22">
         <v>200018</v>
       </c>
-      <c r="B22" s="4">
+      <c r="B22" s="6">
         <v>20099</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D22" s="5">
+      <c r="D22" s="7">
         <v>3002003</v>
       </c>
-      <c r="E22" s="5" t="s">
+      <c r="E22" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="F22" s="8" t="s">
+      <c r="F22" s="10" t="s">
         <v>35</v>
       </c>
       <c r="G22" t="s">
@@ -2478,19 +2478,19 @@
       <c r="A23">
         <v>200019</v>
       </c>
-      <c r="B23" s="4">
+      <c r="B23" s="6">
         <v>20075</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C23" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D23" s="5">
+      <c r="D23" s="7">
         <v>3002001</v>
       </c>
-      <c r="E23" s="5" t="s">
+      <c r="E23" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="F23" s="6" t="s">
+      <c r="F23" s="8" t="s">
         <v>28</v>
       </c>
       <c r="G23" t="s">
@@ -2522,19 +2522,19 @@
       <c r="A24">
         <v>200020</v>
       </c>
-      <c r="B24" s="4">
+      <c r="B24" s="6">
         <v>20075</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C24" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D24" s="5">
+      <c r="D24" s="7">
         <v>3002002</v>
       </c>
-      <c r="E24" s="5" t="s">
+      <c r="E24" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="F24" s="7" t="s">
+      <c r="F24" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G24" t="s">
@@ -2566,19 +2566,19 @@
       <c r="A25">
         <v>200021</v>
       </c>
-      <c r="B25" s="4">
+      <c r="B25" s="6">
         <v>20075</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C25" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D25" s="5">
+      <c r="D25" s="7">
         <v>3002003</v>
       </c>
-      <c r="E25" s="5" t="s">
+      <c r="E25" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="F25" s="8" t="s">
+      <c r="F25" s="10" t="s">
         <v>35</v>
       </c>
       <c r="G25" t="s">
@@ -2610,19 +2610,19 @@
       <c r="A26">
         <v>200022</v>
       </c>
-      <c r="B26" s="4">
+      <c r="B26" s="6">
         <v>20050</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C26" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="D26" s="5">
+      <c r="D26" s="7">
         <v>3002001</v>
       </c>
-      <c r="E26" s="5" t="s">
+      <c r="E26" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="F26" s="6" t="s">
+      <c r="F26" s="8" t="s">
         <v>28</v>
       </c>
       <c r="G26" t="s">
@@ -2654,19 +2654,19 @@
       <c r="A27">
         <v>200023</v>
       </c>
-      <c r="B27" s="4">
+      <c r="B27" s="6">
         <v>20050</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="C27" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="D27" s="5">
+      <c r="D27" s="7">
         <v>3002002</v>
       </c>
-      <c r="E27" s="5" t="s">
+      <c r="E27" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="F27" s="7" t="s">
+      <c r="F27" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G27" t="s">
@@ -2698,19 +2698,19 @@
       <c r="A28">
         <v>200024</v>
       </c>
-      <c r="B28" s="4">
+      <c r="B28" s="6">
         <v>20050</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="C28" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="D28" s="5">
+      <c r="D28" s="7">
         <v>3002003</v>
       </c>
-      <c r="E28" s="5" t="s">
+      <c r="E28" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="F28" s="8" t="s">
+      <c r="F28" s="10" t="s">
         <v>35</v>
       </c>
       <c r="G28" t="s">
@@ -2742,19 +2742,19 @@
       <c r="A29">
         <v>200025</v>
       </c>
-      <c r="B29" s="4">
+      <c r="B29" s="6">
         <v>20025</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="C29" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="D29" s="5">
+      <c r="D29" s="7">
         <v>3002001</v>
       </c>
-      <c r="E29" s="5" t="s">
+      <c r="E29" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="F29" s="6" t="s">
+      <c r="F29" s="8" t="s">
         <v>28</v>
       </c>
       <c r="G29" t="s">
@@ -2786,19 +2786,19 @@
       <c r="A30">
         <v>200026</v>
       </c>
-      <c r="B30" s="4">
+      <c r="B30" s="6">
         <v>20025</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="C30" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="D30" s="5">
+      <c r="D30" s="7">
         <v>3002002</v>
       </c>
-      <c r="E30" s="5" t="s">
+      <c r="E30" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="F30" s="7" t="s">
+      <c r="F30" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G30" t="s">
@@ -2830,19 +2830,19 @@
       <c r="A31">
         <v>200027</v>
       </c>
-      <c r="B31" s="4">
+      <c r="B31" s="6">
         <v>20025</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="C31" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="D31" s="5">
+      <c r="D31" s="7">
         <v>3002003</v>
       </c>
-      <c r="E31" s="5" t="s">
+      <c r="E31" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="F31" s="8" t="s">
+      <c r="F31" s="10" t="s">
         <v>35</v>
       </c>
       <c r="G31" t="s">
@@ -2874,19 +2874,19 @@
       <c r="A32">
         <v>200028</v>
       </c>
-      <c r="B32" s="4">
+      <c r="B32" s="6">
         <v>20001</v>
       </c>
-      <c r="C32" s="4" t="s">
+      <c r="C32" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="D32" s="5">
+      <c r="D32" s="7">
         <v>3002001</v>
       </c>
-      <c r="E32" s="5" t="s">
+      <c r="E32" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="F32" s="6" t="s">
+      <c r="F32" s="8" t="s">
         <v>28</v>
       </c>
       <c r="G32" t="s">
@@ -2918,19 +2918,19 @@
       <c r="A33">
         <v>200029</v>
       </c>
-      <c r="B33" s="4">
+      <c r="B33" s="6">
         <v>20001</v>
       </c>
-      <c r="C33" s="4" t="s">
+      <c r="C33" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="D33" s="5">
+      <c r="D33" s="7">
         <v>3002002</v>
       </c>
-      <c r="E33" s="5" t="s">
+      <c r="E33" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="F33" s="7" t="s">
+      <c r="F33" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G33" t="s">
@@ -2962,19 +2962,19 @@
       <c r="A34">
         <v>200030</v>
       </c>
-      <c r="B34" s="4">
+      <c r="B34" s="6">
         <v>20001</v>
       </c>
-      <c r="C34" s="4" t="s">
+      <c r="C34" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="D34" s="5">
+      <c r="D34" s="7">
         <v>3002003</v>
       </c>
-      <c r="E34" s="5" t="s">
+      <c r="E34" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="F34" s="8" t="s">
+      <c r="F34" s="10" t="s">
         <v>35</v>
       </c>
       <c r="G34" t="s">
@@ -2999,6 +2999,666 @@
         <v>56</v>
       </c>
       <c r="N34">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="35" customFormat="1" ht="16.5" spans="1:14">
+      <c r="A35">
+        <v>200031</v>
+      </c>
+      <c r="B35" s="6">
+        <v>20099</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D35" s="7">
+        <v>30010021</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F35" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G35" t="s">
+        <v>29</v>
+      </c>
+      <c r="H35" t="s">
+        <v>30</v>
+      </c>
+      <c r="I35" t="s">
+        <v>31</v>
+      </c>
+      <c r="J35" t="s">
+        <v>32</v>
+      </c>
+      <c r="K35">
+        <v>8000</v>
+      </c>
+      <c r="L35">
+        <v>12000</v>
+      </c>
+      <c r="M35" t="s">
+        <v>33</v>
+      </c>
+      <c r="N35">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="36" customFormat="1" ht="16.5" spans="1:14">
+      <c r="A36">
+        <v>200032</v>
+      </c>
+      <c r="B36" s="6">
+        <v>20099</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D36" s="7">
+        <v>30010022</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F36" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="G36" t="s">
+        <v>29</v>
+      </c>
+      <c r="H36" t="s">
+        <v>30</v>
+      </c>
+      <c r="I36" t="s">
+        <v>31</v>
+      </c>
+      <c r="J36" t="s">
+        <v>32</v>
+      </c>
+      <c r="K36">
+        <v>8000</v>
+      </c>
+      <c r="L36">
+        <v>12000</v>
+      </c>
+      <c r="M36" t="s">
+        <v>33</v>
+      </c>
+      <c r="N36">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="37" customFormat="1" ht="16.5" spans="1:14">
+      <c r="A37">
+        <v>200033</v>
+      </c>
+      <c r="B37" s="6">
+        <v>20099</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D37" s="7">
+        <v>30010023</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F37" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="G37" t="s">
+        <v>29</v>
+      </c>
+      <c r="H37" t="s">
+        <v>30</v>
+      </c>
+      <c r="I37" t="s">
+        <v>31</v>
+      </c>
+      <c r="J37" t="s">
+        <v>32</v>
+      </c>
+      <c r="K37">
+        <v>8000</v>
+      </c>
+      <c r="L37">
+        <v>12000</v>
+      </c>
+      <c r="M37" t="s">
+        <v>33</v>
+      </c>
+      <c r="N37">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="38" customFormat="1" ht="16.5" spans="1:14">
+      <c r="A38">
+        <v>200034</v>
+      </c>
+      <c r="B38" s="6">
+        <v>20075</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D38" s="7">
+        <v>30010021</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F38" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G38" t="s">
+        <v>29</v>
+      </c>
+      <c r="H38" t="s">
+        <v>37</v>
+      </c>
+      <c r="I38" t="s">
+        <v>38</v>
+      </c>
+      <c r="J38" t="s">
+        <v>39</v>
+      </c>
+      <c r="K38">
+        <v>6000</v>
+      </c>
+      <c r="L38">
+        <v>10000</v>
+      </c>
+      <c r="M38" t="s">
+        <v>40</v>
+      </c>
+      <c r="N38">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="39" customFormat="1" ht="16.5" spans="1:14">
+      <c r="A39">
+        <v>200035</v>
+      </c>
+      <c r="B39" s="6">
+        <v>20075</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D39" s="7">
+        <v>30010022</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F39" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="G39" t="s">
+        <v>29</v>
+      </c>
+      <c r="H39" t="s">
+        <v>37</v>
+      </c>
+      <c r="I39" t="s">
+        <v>38</v>
+      </c>
+      <c r="J39" t="s">
+        <v>41</v>
+      </c>
+      <c r="K39">
+        <v>6000</v>
+      </c>
+      <c r="L39">
+        <v>10000</v>
+      </c>
+      <c r="M39" t="s">
+        <v>40</v>
+      </c>
+      <c r="N39">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="40" customFormat="1" ht="16.5" spans="1:14">
+      <c r="A40">
+        <v>200036</v>
+      </c>
+      <c r="B40" s="6">
+        <v>20075</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D40" s="7">
+        <v>30010023</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F40" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="G40" t="s">
+        <v>29</v>
+      </c>
+      <c r="H40" t="s">
+        <v>37</v>
+      </c>
+      <c r="I40" t="s">
+        <v>38</v>
+      </c>
+      <c r="J40" t="s">
+        <v>41</v>
+      </c>
+      <c r="K40">
+        <v>6000</v>
+      </c>
+      <c r="L40">
+        <v>10000</v>
+      </c>
+      <c r="M40" t="s">
+        <v>40</v>
+      </c>
+      <c r="N40">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="41" customFormat="1" ht="16.5" spans="1:14">
+      <c r="A41">
+        <v>200037</v>
+      </c>
+      <c r="B41" s="6">
+        <v>20050</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D41" s="7">
+        <v>30010021</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F41" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G41" t="s">
+        <v>43</v>
+      </c>
+      <c r="H41" t="s">
+        <v>44</v>
+      </c>
+      <c r="I41" t="s">
+        <v>45</v>
+      </c>
+      <c r="J41" t="s">
+        <v>46</v>
+      </c>
+      <c r="K41">
+        <v>4000</v>
+      </c>
+      <c r="L41">
+        <v>8000</v>
+      </c>
+      <c r="M41" t="s">
+        <v>47</v>
+      </c>
+      <c r="N41">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="42" customFormat="1" ht="16.5" spans="1:14">
+      <c r="A42">
+        <v>200038</v>
+      </c>
+      <c r="B42" s="6">
+        <v>20050</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D42" s="7">
+        <v>30010022</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F42" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="G42" t="s">
+        <v>43</v>
+      </c>
+      <c r="H42" t="s">
+        <v>44</v>
+      </c>
+      <c r="I42" t="s">
+        <v>45</v>
+      </c>
+      <c r="J42" t="s">
+        <v>46</v>
+      </c>
+      <c r="K42">
+        <v>4000</v>
+      </c>
+      <c r="L42">
+        <v>8000</v>
+      </c>
+      <c r="M42" t="s">
+        <v>47</v>
+      </c>
+      <c r="N42">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="43" customFormat="1" ht="16.5" spans="1:14">
+      <c r="A43">
+        <v>200039</v>
+      </c>
+      <c r="B43" s="6">
+        <v>20050</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D43" s="7">
+        <v>30010023</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F43" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="G43" t="s">
+        <v>43</v>
+      </c>
+      <c r="H43" t="s">
+        <v>44</v>
+      </c>
+      <c r="I43" t="s">
+        <v>45</v>
+      </c>
+      <c r="J43" t="s">
+        <v>46</v>
+      </c>
+      <c r="K43">
+        <v>4000</v>
+      </c>
+      <c r="L43">
+        <v>8000</v>
+      </c>
+      <c r="M43" t="s">
+        <v>47</v>
+      </c>
+      <c r="N43">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="44" customFormat="1" ht="16.5" spans="1:14">
+      <c r="A44">
+        <v>200040</v>
+      </c>
+      <c r="B44" s="6">
+        <v>20025</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D44" s="7">
+        <v>30010021</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F44" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G44" t="s">
+        <v>43</v>
+      </c>
+      <c r="H44" t="s">
+        <v>49</v>
+      </c>
+      <c r="I44" t="s">
+        <v>50</v>
+      </c>
+      <c r="J44" t="s">
+        <v>51</v>
+      </c>
+      <c r="K44">
+        <v>2000</v>
+      </c>
+      <c r="L44">
+        <v>6000</v>
+      </c>
+      <c r="M44" t="s">
+        <v>52</v>
+      </c>
+      <c r="N44">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="45" customFormat="1" ht="16.5" spans="1:14">
+      <c r="A45">
+        <v>200041</v>
+      </c>
+      <c r="B45" s="6">
+        <v>20025</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D45" s="7">
+        <v>30010022</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F45" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="G45" t="s">
+        <v>43</v>
+      </c>
+      <c r="H45" t="s">
+        <v>49</v>
+      </c>
+      <c r="I45" t="s">
+        <v>50</v>
+      </c>
+      <c r="J45" t="s">
+        <v>51</v>
+      </c>
+      <c r="K45">
+        <v>2000</v>
+      </c>
+      <c r="L45">
+        <v>6000</v>
+      </c>
+      <c r="M45" t="s">
+        <v>52</v>
+      </c>
+      <c r="N45">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="46" customFormat="1" ht="16.5" spans="1:14">
+      <c r="A46">
+        <v>200042</v>
+      </c>
+      <c r="B46" s="6">
+        <v>20025</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D46" s="7">
+        <v>30010023</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F46" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="G46" t="s">
+        <v>43</v>
+      </c>
+      <c r="H46" t="s">
+        <v>49</v>
+      </c>
+      <c r="I46" t="s">
+        <v>50</v>
+      </c>
+      <c r="J46" t="s">
+        <v>51</v>
+      </c>
+      <c r="K46">
+        <v>2000</v>
+      </c>
+      <c r="L46">
+        <v>6000</v>
+      </c>
+      <c r="M46" t="s">
+        <v>52</v>
+      </c>
+      <c r="N46">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="47" customFormat="1" ht="16.5" spans="1:14">
+      <c r="A47">
+        <v>200043</v>
+      </c>
+      <c r="B47" s="6">
+        <v>20001</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D47" s="7">
+        <v>30010021</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F47" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G47" t="s">
+        <v>43</v>
+      </c>
+      <c r="H47" t="s">
+        <v>54</v>
+      </c>
+      <c r="I47" t="s">
+        <v>55</v>
+      </c>
+      <c r="J47" t="s">
+        <v>51</v>
+      </c>
+      <c r="K47">
+        <v>1000</v>
+      </c>
+      <c r="L47">
+        <v>4000</v>
+      </c>
+      <c r="M47" t="s">
+        <v>56</v>
+      </c>
+      <c r="N47">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="48" customFormat="1" ht="16.5" spans="1:14">
+      <c r="A48">
+        <v>200044</v>
+      </c>
+      <c r="B48" s="6">
+        <v>20001</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D48" s="7">
+        <v>30010022</v>
+      </c>
+      <c r="E48" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F48" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="G48" t="s">
+        <v>43</v>
+      </c>
+      <c r="H48" t="s">
+        <v>54</v>
+      </c>
+      <c r="I48" t="s">
+        <v>55</v>
+      </c>
+      <c r="J48" t="s">
+        <v>51</v>
+      </c>
+      <c r="K48">
+        <v>1000</v>
+      </c>
+      <c r="L48">
+        <v>4000</v>
+      </c>
+      <c r="M48" t="s">
+        <v>56</v>
+      </c>
+      <c r="N48">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="49" customFormat="1" ht="16.5" spans="1:14">
+      <c r="A49">
+        <v>200045</v>
+      </c>
+      <c r="B49" s="6">
+        <v>20001</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D49" s="7">
+        <v>30010023</v>
+      </c>
+      <c r="E49" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F49" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="G49" t="s">
+        <v>43</v>
+      </c>
+      <c r="H49" t="s">
+        <v>54</v>
+      </c>
+      <c r="I49" t="s">
+        <v>55</v>
+      </c>
+      <c r="J49" t="s">
+        <v>51</v>
+      </c>
+      <c r="K49">
+        <v>1000</v>
+      </c>
+      <c r="L49">
+        <v>4000</v>
+      </c>
+      <c r="M49" t="s">
+        <v>56</v>
+      </c>
+      <c r="N49">
         <v>4000</v>
       </c>
     </row>

--- a/poker/resources/sample/RobotAction_Chess.xlsx
+++ b/poker/resources/sample/RobotAction_Chess.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="ChessRobot" sheetId="1" r:id="rId1"/>
@@ -150,7 +150,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="71">
   <si>
     <t>序列</t>
   </si>
@@ -324,6 +324,45 @@
   </si>
   <si>
     <t>德州</t>
+  </si>
+  <si>
+    <t>南方前进</t>
+  </si>
+  <si>
+    <t>南方前进基础场</t>
+  </si>
+  <si>
+    <t>10000_10000</t>
+  </si>
+  <si>
+    <t>8000_10000</t>
+  </si>
+  <si>
+    <t>南方前进中级场</t>
+  </si>
+  <si>
+    <t>南方前进高级场</t>
+  </si>
+  <si>
+    <t>9500_10000</t>
+  </si>
+  <si>
+    <t>7500_10000</t>
+  </si>
+  <si>
+    <t>9000_10000</t>
+  </si>
+  <si>
+    <t>7000_10000</t>
+  </si>
+  <si>
+    <t>8500_10000</t>
+  </si>
+  <si>
+    <t>6500_10000</t>
+  </si>
+  <si>
+    <t>6000_10000</t>
   </si>
 </sst>
 </file>
@@ -521,6 +560,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -534,18 +585,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -996,6 +1035,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1008,17 +1049,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1545,12 +1584,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N34"/>
+  <dimension ref="A1:N49"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="3" width="10.875" customWidth="1"/>
     <col min="4" max="5" width="9.375" customWidth="1"/>
-    <col min="6" max="6" width="11.25" customWidth="1"/>
+    <col min="6" max="6" width="15.2833333333333" customWidth="1"/>
     <col min="7" max="7" width="26.625" customWidth="1"/>
     <col min="8" max="8" width="30.2916666666667" customWidth="1"/>
     <col min="9" max="9" width="31.9083333333333" customWidth="1"/>
@@ -1584,19 +1623,19 @@
       <c r="I1" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="K1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="L1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="M1" s="10" t="s">
+      <c r="M1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="N1" s="10" t="s">
+      <c r="N1" s="3" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1607,18 +1646,18 @@
       <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="2"/>
+      <c r="C2" s="4"/>
       <c r="D2" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="2"/>
+      <c r="F2" s="4"/>
       <c r="G2" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="5" t="s">
         <v>13</v>
       </c>
       <c r="J2" t="s">
@@ -1641,15 +1680,15 @@
       <c r="A3" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2" t="s">
+      <c r="C3" s="4"/>
+      <c r="D3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
       <c r="G3" t="s">
         <v>18</v>
       </c>
@@ -1675,30 +1714,30 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" ht="16.5" spans="2:6">
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
+    <row r="4" ht="16.5" spans="1:14">
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
     </row>
     <row r="5" ht="16.5" spans="1:14">
       <c r="A5">
         <v>200001</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="6">
         <v>20099</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="7">
         <v>3001001</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="8" t="s">
         <v>28</v>
       </c>
       <c r="G5" t="s">
@@ -1730,19 +1769,19 @@
       <c r="A6">
         <v>200002</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6" s="6">
         <v>20099</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="7">
         <v>3001002</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G6" t="s">
@@ -1774,19 +1813,19 @@
       <c r="A7">
         <v>200003</v>
       </c>
-      <c r="B7" s="4">
+      <c r="B7" s="6">
         <v>20099</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="7">
         <v>3001003</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="F7" s="10" t="s">
         <v>35</v>
       </c>
       <c r="G7" t="s">
@@ -1818,19 +1857,19 @@
       <c r="A8">
         <v>200004</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8" s="6">
         <v>20075</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8" s="7">
         <v>3001001</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F8" s="8" t="s">
         <v>28</v>
       </c>
       <c r="G8" t="s">
@@ -1862,19 +1901,19 @@
       <c r="A9">
         <v>200005</v>
       </c>
-      <c r="B9" s="4">
+      <c r="B9" s="6">
         <v>20075</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D9" s="7">
         <v>3001002</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G9" t="s">
@@ -1906,19 +1945,19 @@
       <c r="A10">
         <v>200006</v>
       </c>
-      <c r="B10" s="4">
+      <c r="B10" s="6">
         <v>20075</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="5">
+      <c r="D10" s="7">
         <v>3001003</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="F10" s="10" t="s">
         <v>35</v>
       </c>
       <c r="G10" t="s">
@@ -1950,19 +1989,19 @@
       <c r="A11">
         <v>200007</v>
       </c>
-      <c r="B11" s="4">
+      <c r="B11" s="6">
         <v>20050</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="D11" s="5">
+      <c r="D11" s="7">
         <v>3001001</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="F11" s="6" t="s">
+      <c r="F11" s="8" t="s">
         <v>28</v>
       </c>
       <c r="G11" t="s">
@@ -1994,19 +2033,19 @@
       <c r="A12">
         <v>200008</v>
       </c>
-      <c r="B12" s="4">
+      <c r="B12" s="6">
         <v>20050</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="D12" s="5">
+      <c r="D12" s="7">
         <v>3001002</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E12" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G12" t="s">
@@ -2038,19 +2077,19 @@
       <c r="A13">
         <v>200009</v>
       </c>
-      <c r="B13" s="4">
+      <c r="B13" s="6">
         <v>20050</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="D13" s="5">
+      <c r="D13" s="7">
         <v>3001003</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="E13" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="F13" s="8" t="s">
+      <c r="F13" s="10" t="s">
         <v>35</v>
       </c>
       <c r="G13" t="s">
@@ -2082,19 +2121,19 @@
       <c r="A14">
         <v>200010</v>
       </c>
-      <c r="B14" s="4">
+      <c r="B14" s="6">
         <v>20025</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="D14" s="5">
+      <c r="D14" s="7">
         <v>3001001</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="F14" s="6" t="s">
+      <c r="F14" s="8" t="s">
         <v>28</v>
       </c>
       <c r="G14" t="s">
@@ -2126,19 +2165,19 @@
       <c r="A15">
         <v>200011</v>
       </c>
-      <c r="B15" s="4">
+      <c r="B15" s="6">
         <v>20025</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="D15" s="5">
+      <c r="D15" s="7">
         <v>3001002</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="E15" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="F15" s="7" t="s">
+      <c r="F15" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G15" t="s">
@@ -2170,19 +2209,19 @@
       <c r="A16">
         <v>200012</v>
       </c>
-      <c r="B16" s="4">
+      <c r="B16" s="6">
         <v>20025</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="D16" s="5">
+      <c r="D16" s="7">
         <v>3001003</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="E16" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="F16" s="8" t="s">
+      <c r="F16" s="10" t="s">
         <v>35</v>
       </c>
       <c r="G16" t="s">
@@ -2214,19 +2253,19 @@
       <c r="A17">
         <v>200013</v>
       </c>
-      <c r="B17" s="4">
+      <c r="B17" s="6">
         <v>20001</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="D17" s="5">
+      <c r="D17" s="7">
         <v>3001001</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="E17" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="F17" s="6" t="s">
+      <c r="F17" s="8" t="s">
         <v>28</v>
       </c>
       <c r="G17" t="s">
@@ -2258,19 +2297,19 @@
       <c r="A18">
         <v>200014</v>
       </c>
-      <c r="B18" s="4">
+      <c r="B18" s="6">
         <v>20001</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="D18" s="5">
+      <c r="D18" s="7">
         <v>3001002</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="E18" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="F18" s="7" t="s">
+      <c r="F18" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G18" t="s">
@@ -2302,19 +2341,19 @@
       <c r="A19">
         <v>200015</v>
       </c>
-      <c r="B19" s="4">
+      <c r="B19" s="6">
         <v>20001</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="D19" s="5">
+      <c r="D19" s="7">
         <v>3001003</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="E19" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="F19" s="8" t="s">
+      <c r="F19" s="10" t="s">
         <v>35</v>
       </c>
       <c r="G19" t="s">
@@ -2346,19 +2385,19 @@
       <c r="A20">
         <v>200016</v>
       </c>
-      <c r="B20" s="4">
+      <c r="B20" s="6">
         <v>20099</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D20" s="5">
+      <c r="D20" s="7">
         <v>3002001</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="E20" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="F20" s="6" t="s">
+      <c r="F20" s="8" t="s">
         <v>28</v>
       </c>
       <c r="G20" t="s">
@@ -2390,19 +2429,19 @@
       <c r="A21">
         <v>200017</v>
       </c>
-      <c r="B21" s="4">
+      <c r="B21" s="6">
         <v>20099</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D21" s="5">
+      <c r="D21" s="7">
         <v>3002002</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="E21" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="F21" s="7" t="s">
+      <c r="F21" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G21" t="s">
@@ -2434,19 +2473,19 @@
       <c r="A22">
         <v>200018</v>
       </c>
-      <c r="B22" s="4">
+      <c r="B22" s="6">
         <v>20099</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D22" s="5">
+      <c r="D22" s="7">
         <v>3002003</v>
       </c>
-      <c r="E22" s="5" t="s">
+      <c r="E22" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="F22" s="8" t="s">
+      <c r="F22" s="10" t="s">
         <v>35</v>
       </c>
       <c r="G22" t="s">
@@ -2478,19 +2517,19 @@
       <c r="A23">
         <v>200019</v>
       </c>
-      <c r="B23" s="4">
+      <c r="B23" s="6">
         <v>20075</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C23" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D23" s="5">
+      <c r="D23" s="7">
         <v>3002001</v>
       </c>
-      <c r="E23" s="5" t="s">
+      <c r="E23" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="F23" s="6" t="s">
+      <c r="F23" s="8" t="s">
         <v>28</v>
       </c>
       <c r="G23" t="s">
@@ -2522,19 +2561,19 @@
       <c r="A24">
         <v>200020</v>
       </c>
-      <c r="B24" s="4">
+      <c r="B24" s="6">
         <v>20075</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C24" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D24" s="5">
+      <c r="D24" s="7">
         <v>3002002</v>
       </c>
-      <c r="E24" s="5" t="s">
+      <c r="E24" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="F24" s="7" t="s">
+      <c r="F24" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G24" t="s">
@@ -2566,19 +2605,19 @@
       <c r="A25">
         <v>200021</v>
       </c>
-      <c r="B25" s="4">
+      <c r="B25" s="6">
         <v>20075</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C25" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D25" s="5">
+      <c r="D25" s="7">
         <v>3002003</v>
       </c>
-      <c r="E25" s="5" t="s">
+      <c r="E25" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="F25" s="8" t="s">
+      <c r="F25" s="10" t="s">
         <v>35</v>
       </c>
       <c r="G25" t="s">
@@ -2610,19 +2649,19 @@
       <c r="A26">
         <v>200022</v>
       </c>
-      <c r="B26" s="4">
+      <c r="B26" s="6">
         <v>20050</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C26" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="D26" s="5">
+      <c r="D26" s="7">
         <v>3002001</v>
       </c>
-      <c r="E26" s="5" t="s">
+      <c r="E26" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="F26" s="6" t="s">
+      <c r="F26" s="8" t="s">
         <v>28</v>
       </c>
       <c r="G26" t="s">
@@ -2654,19 +2693,19 @@
       <c r="A27">
         <v>200023</v>
       </c>
-      <c r="B27" s="4">
+      <c r="B27" s="6">
         <v>20050</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="C27" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="D27" s="5">
+      <c r="D27" s="7">
         <v>3002002</v>
       </c>
-      <c r="E27" s="5" t="s">
+      <c r="E27" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="F27" s="7" t="s">
+      <c r="F27" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G27" t="s">
@@ -2698,19 +2737,19 @@
       <c r="A28">
         <v>200024</v>
       </c>
-      <c r="B28" s="4">
+      <c r="B28" s="6">
         <v>20050</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="C28" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="D28" s="5">
+      <c r="D28" s="7">
         <v>3002003</v>
       </c>
-      <c r="E28" s="5" t="s">
+      <c r="E28" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="F28" s="8" t="s">
+      <c r="F28" s="10" t="s">
         <v>35</v>
       </c>
       <c r="G28" t="s">
@@ -2742,19 +2781,19 @@
       <c r="A29">
         <v>200025</v>
       </c>
-      <c r="B29" s="4">
+      <c r="B29" s="6">
         <v>20025</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="C29" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="D29" s="5">
+      <c r="D29" s="7">
         <v>3002001</v>
       </c>
-      <c r="E29" s="5" t="s">
+      <c r="E29" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="F29" s="6" t="s">
+      <c r="F29" s="8" t="s">
         <v>28</v>
       </c>
       <c r="G29" t="s">
@@ -2786,19 +2825,19 @@
       <c r="A30">
         <v>200026</v>
       </c>
-      <c r="B30" s="4">
+      <c r="B30" s="6">
         <v>20025</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="C30" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="D30" s="5">
+      <c r="D30" s="7">
         <v>3002002</v>
       </c>
-      <c r="E30" s="5" t="s">
+      <c r="E30" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="F30" s="7" t="s">
+      <c r="F30" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G30" t="s">
@@ -2830,19 +2869,19 @@
       <c r="A31">
         <v>200027</v>
       </c>
-      <c r="B31" s="4">
+      <c r="B31" s="6">
         <v>20025</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="C31" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="D31" s="5">
+      <c r="D31" s="7">
         <v>3002003</v>
       </c>
-      <c r="E31" s="5" t="s">
+      <c r="E31" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="F31" s="8" t="s">
+      <c r="F31" s="10" t="s">
         <v>35</v>
       </c>
       <c r="G31" t="s">
@@ -2874,19 +2913,19 @@
       <c r="A32">
         <v>200028</v>
       </c>
-      <c r="B32" s="4">
+      <c r="B32" s="6">
         <v>20001</v>
       </c>
-      <c r="C32" s="4" t="s">
+      <c r="C32" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="D32" s="5">
+      <c r="D32" s="7">
         <v>3002001</v>
       </c>
-      <c r="E32" s="5" t="s">
+      <c r="E32" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="F32" s="6" t="s">
+      <c r="F32" s="8" t="s">
         <v>28</v>
       </c>
       <c r="G32" t="s">
@@ -2918,19 +2957,19 @@
       <c r="A33">
         <v>200029</v>
       </c>
-      <c r="B33" s="4">
+      <c r="B33" s="6">
         <v>20001</v>
       </c>
-      <c r="C33" s="4" t="s">
+      <c r="C33" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="D33" s="5">
+      <c r="D33" s="7">
         <v>3002002</v>
       </c>
-      <c r="E33" s="5" t="s">
+      <c r="E33" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="F33" s="7" t="s">
+      <c r="F33" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G33" t="s">
@@ -2962,19 +3001,19 @@
       <c r="A34">
         <v>200030</v>
       </c>
-      <c r="B34" s="4">
+      <c r="B34" s="6">
         <v>20001</v>
       </c>
-      <c r="C34" s="4" t="s">
+      <c r="C34" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="D34" s="5">
+      <c r="D34" s="7">
         <v>3002003</v>
       </c>
-      <c r="E34" s="5" t="s">
+      <c r="E34" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="F34" s="8" t="s">
+      <c r="F34" s="10" t="s">
         <v>35</v>
       </c>
       <c r="G34" t="s">
@@ -3000,6 +3039,441 @@
       </c>
       <c r="N34">
         <v>4000</v>
+      </c>
+    </row>
+    <row r="35" ht="16.5" spans="1:14">
+      <c r="A35">
+        <v>200031</v>
+      </c>
+      <c r="B35" s="6">
+        <v>20099</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D35">
+        <v>3004001</v>
+      </c>
+      <c r="E35" t="s">
+        <v>58</v>
+      </c>
+      <c r="F35" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="G35" t="s">
+        <v>29</v>
+      </c>
+      <c r="H35" t="s">
+        <v>60</v>
+      </c>
+      <c r="I35" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="36" ht="16.5" spans="1:14">
+      <c r="A36">
+        <v>200032</v>
+      </c>
+      <c r="B36" s="6">
+        <v>20099</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D36">
+        <v>3004002</v>
+      </c>
+      <c r="E36" t="s">
+        <v>58</v>
+      </c>
+      <c r="F36" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="G36" t="s">
+        <v>29</v>
+      </c>
+      <c r="H36" t="s">
+        <v>60</v>
+      </c>
+      <c r="I36" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="37" ht="16.5" spans="1:14">
+      <c r="A37">
+        <v>200033</v>
+      </c>
+      <c r="B37" s="6">
+        <v>20099</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D37">
+        <v>3004003</v>
+      </c>
+      <c r="E37" t="s">
+        <v>58</v>
+      </c>
+      <c r="F37" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="G37" t="s">
+        <v>29</v>
+      </c>
+      <c r="H37" t="s">
+        <v>60</v>
+      </c>
+      <c r="I37" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="38" ht="16.5" spans="1:14">
+      <c r="A38">
+        <v>200034</v>
+      </c>
+      <c r="B38" s="6">
+        <v>20075</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D38">
+        <v>3004001</v>
+      </c>
+      <c r="E38" t="s">
+        <v>58</v>
+      </c>
+      <c r="F38" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="G38" t="s">
+        <v>29</v>
+      </c>
+      <c r="H38" t="s">
+        <v>64</v>
+      </c>
+      <c r="I38" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="39" ht="16.5" spans="1:14">
+      <c r="A39">
+        <v>200035</v>
+      </c>
+      <c r="B39" s="6">
+        <v>20075</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D39">
+        <v>3004002</v>
+      </c>
+      <c r="E39" t="s">
+        <v>58</v>
+      </c>
+      <c r="F39" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="G39" t="s">
+        <v>29</v>
+      </c>
+      <c r="H39" t="s">
+        <v>64</v>
+      </c>
+      <c r="I39" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="40" ht="16.5" spans="1:14">
+      <c r="A40">
+        <v>200036</v>
+      </c>
+      <c r="B40" s="6">
+        <v>20075</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D40">
+        <v>3004003</v>
+      </c>
+      <c r="E40" t="s">
+        <v>58</v>
+      </c>
+      <c r="F40" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="G40" t="s">
+        <v>29</v>
+      </c>
+      <c r="H40" t="s">
+        <v>64</v>
+      </c>
+      <c r="I40" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="41" ht="16.5" spans="1:14">
+      <c r="A41">
+        <v>200037</v>
+      </c>
+      <c r="B41" s="6">
+        <v>20050</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D41">
+        <v>3004001</v>
+      </c>
+      <c r="E41" t="s">
+        <v>58</v>
+      </c>
+      <c r="F41" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="G41" t="s">
+        <v>43</v>
+      </c>
+      <c r="H41" t="s">
+        <v>66</v>
+      </c>
+      <c r="I41" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="42" ht="16.5" spans="1:14">
+      <c r="A42">
+        <v>200038</v>
+      </c>
+      <c r="B42" s="6">
+        <v>20050</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D42">
+        <v>3004002</v>
+      </c>
+      <c r="E42" t="s">
+        <v>58</v>
+      </c>
+      <c r="F42" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="G42" t="s">
+        <v>43</v>
+      </c>
+      <c r="H42" t="s">
+        <v>66</v>
+      </c>
+      <c r="I42" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="43" ht="16.5" spans="1:14">
+      <c r="A43">
+        <v>200039</v>
+      </c>
+      <c r="B43" s="6">
+        <v>20050</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D43">
+        <v>3004003</v>
+      </c>
+      <c r="E43" t="s">
+        <v>58</v>
+      </c>
+      <c r="F43" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="G43" t="s">
+        <v>43</v>
+      </c>
+      <c r="H43" t="s">
+        <v>66</v>
+      </c>
+      <c r="I43" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="44" ht="16.5" spans="1:14">
+      <c r="A44">
+        <v>200040</v>
+      </c>
+      <c r="B44" s="6">
+        <v>20025</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D44">
+        <v>3004001</v>
+      </c>
+      <c r="E44" t="s">
+        <v>58</v>
+      </c>
+      <c r="F44" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="G44" t="s">
+        <v>43</v>
+      </c>
+      <c r="H44" t="s">
+        <v>68</v>
+      </c>
+      <c r="I44" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="45" ht="16.5" spans="1:14">
+      <c r="A45">
+        <v>200041</v>
+      </c>
+      <c r="B45" s="6">
+        <v>20025</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D45">
+        <v>3004002</v>
+      </c>
+      <c r="E45" t="s">
+        <v>58</v>
+      </c>
+      <c r="F45" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="G45" t="s">
+        <v>43</v>
+      </c>
+      <c r="H45" t="s">
+        <v>68</v>
+      </c>
+      <c r="I45" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="46" ht="16.5" spans="1:14">
+      <c r="A46">
+        <v>200042</v>
+      </c>
+      <c r="B46" s="6">
+        <v>20025</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D46">
+        <v>3004003</v>
+      </c>
+      <c r="E46" t="s">
+        <v>58</v>
+      </c>
+      <c r="F46" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="G46" t="s">
+        <v>43</v>
+      </c>
+      <c r="H46" t="s">
+        <v>68</v>
+      </c>
+      <c r="I46" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="47" ht="16.5" spans="1:14">
+      <c r="A47">
+        <v>200043</v>
+      </c>
+      <c r="B47" s="6">
+        <v>20001</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D47">
+        <v>3004001</v>
+      </c>
+      <c r="E47" t="s">
+        <v>58</v>
+      </c>
+      <c r="F47" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="G47" t="s">
+        <v>43</v>
+      </c>
+      <c r="H47" t="s">
+        <v>61</v>
+      </c>
+      <c r="I47" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="48" ht="16.5" spans="1:14">
+      <c r="A48">
+        <v>200044</v>
+      </c>
+      <c r="B48" s="6">
+        <v>20001</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D48">
+        <v>3004002</v>
+      </c>
+      <c r="E48" t="s">
+        <v>58</v>
+      </c>
+      <c r="F48" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="G48" t="s">
+        <v>43</v>
+      </c>
+      <c r="H48" t="s">
+        <v>61</v>
+      </c>
+      <c r="I48" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="49" ht="16.5" spans="1:9">
+      <c r="A49">
+        <v>200045</v>
+      </c>
+      <c r="B49" s="6">
+        <v>20001</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D49">
+        <v>3004003</v>
+      </c>
+      <c r="E49" t="s">
+        <v>58</v>
+      </c>
+      <c r="F49" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="G49" t="s">
+        <v>43</v>
+      </c>
+      <c r="H49" t="s">
+        <v>61</v>
+      </c>
+      <c r="I49" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>

--- a/poker/resources/sample/RobotAction_Chess.xlsx
+++ b/poker/resources/sample/RobotAction_Chess.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="ChessRobot" sheetId="1" r:id="rId1"/>
@@ -150,7 +150,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="58">
   <si>
     <t>序列</t>
   </si>
@@ -324,45 +324,6 @@
   </si>
   <si>
     <t>德州</t>
-  </si>
-  <si>
-    <t>南方前进</t>
-  </si>
-  <si>
-    <t>南方前进基础场</t>
-  </si>
-  <si>
-    <t>10000_10000</t>
-  </si>
-  <si>
-    <t>8000_10000</t>
-  </si>
-  <si>
-    <t>南方前进中级场</t>
-  </si>
-  <si>
-    <t>南方前进高级场</t>
-  </si>
-  <si>
-    <t>9500_10000</t>
-  </si>
-  <si>
-    <t>7500_10000</t>
-  </si>
-  <si>
-    <t>9000_10000</t>
-  </si>
-  <si>
-    <t>7000_10000</t>
-  </si>
-  <si>
-    <t>8500_10000</t>
-  </si>
-  <si>
-    <t>6500_10000</t>
-  </si>
-  <si>
-    <t>6000_10000</t>
   </si>
 </sst>
 </file>
@@ -560,6 +521,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -567,24 +546,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1035,8 +996,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1049,15 +1008,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1584,12 +1545,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N49"/>
+  <dimension ref="A1:N34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="3" width="10.875" customWidth="1"/>
     <col min="4" max="5" width="9.375" customWidth="1"/>
-    <col min="6" max="6" width="15.2833333333333" customWidth="1"/>
+    <col min="6" max="6" width="11.25" customWidth="1"/>
     <col min="7" max="7" width="26.625" customWidth="1"/>
     <col min="8" max="8" width="30.2916666666667" customWidth="1"/>
     <col min="9" max="9" width="31.9083333333333" customWidth="1"/>
@@ -1623,19 +1584,19 @@
       <c r="I1" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="10" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1646,18 +1607,18 @@
       <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="4"/>
+      <c r="C2" s="2"/>
       <c r="D2" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="4"/>
+      <c r="F2" s="2"/>
       <c r="G2" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="I2" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J2" t="s">
@@ -1680,15 +1641,15 @@
       <c r="A3" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4" t="s">
+      <c r="C3" s="2"/>
+      <c r="D3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
       <c r="G3" t="s">
         <v>18</v>
       </c>
@@ -1714,30 +1675,30 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" ht="16.5" spans="1:14">
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
+    <row r="4" ht="16.5" spans="2:6">
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
     </row>
     <row r="5" ht="16.5" spans="1:14">
       <c r="A5">
         <v>200001</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="4">
         <v>20099</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="5">
         <v>3001001</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="F5" s="6" t="s">
         <v>28</v>
       </c>
       <c r="G5" t="s">
@@ -1769,19 +1730,19 @@
       <c r="A6">
         <v>200002</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="4">
         <v>20099</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="5">
         <v>3001002</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="F6" s="7" t="s">
         <v>34</v>
       </c>
       <c r="G6" t="s">
@@ -1813,19 +1774,19 @@
       <c r="A7">
         <v>200003</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="4">
         <v>20099</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="5">
         <v>3001003</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="F7" s="10" t="s">
+      <c r="F7" s="8" t="s">
         <v>35</v>
       </c>
       <c r="G7" t="s">
@@ -1857,19 +1818,19 @@
       <c r="A8">
         <v>200004</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="4">
         <v>20075</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="5">
         <v>3001001</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="F8" s="6" t="s">
         <v>28</v>
       </c>
       <c r="G8" t="s">
@@ -1901,19 +1862,19 @@
       <c r="A9">
         <v>200005</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="4">
         <v>20075</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D9" s="5">
         <v>3001002</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="F9" s="9" t="s">
+      <c r="F9" s="7" t="s">
         <v>34</v>
       </c>
       <c r="G9" t="s">
@@ -1945,19 +1906,19 @@
       <c r="A10">
         <v>200006</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="4">
         <v>20075</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D10" s="5">
         <v>3001003</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="F10" s="10" t="s">
+      <c r="F10" s="8" t="s">
         <v>35</v>
       </c>
       <c r="G10" t="s">
@@ -1989,19 +1950,19 @@
       <c r="A11">
         <v>200007</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="4">
         <v>20050</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D11" s="7">
+      <c r="D11" s="5">
         <v>3001001</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="F11" s="8" t="s">
+      <c r="F11" s="6" t="s">
         <v>28</v>
       </c>
       <c r="G11" t="s">
@@ -2033,19 +1994,19 @@
       <c r="A12">
         <v>200008</v>
       </c>
-      <c r="B12" s="6">
+      <c r="B12" s="4">
         <v>20050</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D12" s="7">
+      <c r="D12" s="5">
         <v>3001002</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="E12" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="F12" s="9" t="s">
+      <c r="F12" s="7" t="s">
         <v>34</v>
       </c>
       <c r="G12" t="s">
@@ -2077,19 +2038,19 @@
       <c r="A13">
         <v>200009</v>
       </c>
-      <c r="B13" s="6">
+      <c r="B13" s="4">
         <v>20050</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D13" s="7">
+      <c r="D13" s="5">
         <v>3001003</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E13" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="F13" s="10" t="s">
+      <c r="F13" s="8" t="s">
         <v>35</v>
       </c>
       <c r="G13" t="s">
@@ -2121,19 +2082,19 @@
       <c r="A14">
         <v>200010</v>
       </c>
-      <c r="B14" s="6">
+      <c r="B14" s="4">
         <v>20025</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D14" s="7">
+      <c r="D14" s="5">
         <v>3001001</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="E14" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="F14" s="8" t="s">
+      <c r="F14" s="6" t="s">
         <v>28</v>
       </c>
       <c r="G14" t="s">
@@ -2165,19 +2126,19 @@
       <c r="A15">
         <v>200011</v>
       </c>
-      <c r="B15" s="6">
+      <c r="B15" s="4">
         <v>20025</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D15" s="7">
+      <c r="D15" s="5">
         <v>3001002</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="E15" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="F15" s="9" t="s">
+      <c r="F15" s="7" t="s">
         <v>34</v>
       </c>
       <c r="G15" t="s">
@@ -2209,19 +2170,19 @@
       <c r="A16">
         <v>200012</v>
       </c>
-      <c r="B16" s="6">
+      <c r="B16" s="4">
         <v>20025</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D16" s="7">
+      <c r="D16" s="5">
         <v>3001003</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="E16" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="F16" s="10" t="s">
+      <c r="F16" s="8" t="s">
         <v>35</v>
       </c>
       <c r="G16" t="s">
@@ -2253,19 +2214,19 @@
       <c r="A17">
         <v>200013</v>
       </c>
-      <c r="B17" s="6">
+      <c r="B17" s="4">
         <v>20001</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="D17" s="7">
+      <c r="D17" s="5">
         <v>3001001</v>
       </c>
-      <c r="E17" s="7" t="s">
+      <c r="E17" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="F17" s="8" t="s">
+      <c r="F17" s="6" t="s">
         <v>28</v>
       </c>
       <c r="G17" t="s">
@@ -2297,19 +2258,19 @@
       <c r="A18">
         <v>200014</v>
       </c>
-      <c r="B18" s="6">
+      <c r="B18" s="4">
         <v>20001</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="D18" s="7">
+      <c r="D18" s="5">
         <v>3001002</v>
       </c>
-      <c r="E18" s="7" t="s">
+      <c r="E18" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="F18" s="9" t="s">
+      <c r="F18" s="7" t="s">
         <v>34</v>
       </c>
       <c r="G18" t="s">
@@ -2341,19 +2302,19 @@
       <c r="A19">
         <v>200015</v>
       </c>
-      <c r="B19" s="6">
+      <c r="B19" s="4">
         <v>20001</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="D19" s="7">
+      <c r="D19" s="5">
         <v>3001003</v>
       </c>
-      <c r="E19" s="7" t="s">
+      <c r="E19" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="F19" s="10" t="s">
+      <c r="F19" s="8" t="s">
         <v>35</v>
       </c>
       <c r="G19" t="s">
@@ -2385,19 +2346,19 @@
       <c r="A20">
         <v>200016</v>
       </c>
-      <c r="B20" s="6">
+      <c r="B20" s="4">
         <v>20099</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D20" s="7">
+      <c r="D20" s="5">
         <v>3002001</v>
       </c>
-      <c r="E20" s="7" t="s">
+      <c r="E20" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="F20" s="8" t="s">
+      <c r="F20" s="6" t="s">
         <v>28</v>
       </c>
       <c r="G20" t="s">
@@ -2429,19 +2390,19 @@
       <c r="A21">
         <v>200017</v>
       </c>
-      <c r="B21" s="6">
+      <c r="B21" s="4">
         <v>20099</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D21" s="7">
+      <c r="D21" s="5">
         <v>3002002</v>
       </c>
-      <c r="E21" s="7" t="s">
+      <c r="E21" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="F21" s="9" t="s">
+      <c r="F21" s="7" t="s">
         <v>34</v>
       </c>
       <c r="G21" t="s">
@@ -2473,19 +2434,19 @@
       <c r="A22">
         <v>200018</v>
       </c>
-      <c r="B22" s="6">
+      <c r="B22" s="4">
         <v>20099</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D22" s="7">
+      <c r="D22" s="5">
         <v>3002003</v>
       </c>
-      <c r="E22" s="7" t="s">
+      <c r="E22" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="F22" s="10" t="s">
+      <c r="F22" s="8" t="s">
         <v>35</v>
       </c>
       <c r="G22" t="s">
@@ -2517,19 +2478,19 @@
       <c r="A23">
         <v>200019</v>
       </c>
-      <c r="B23" s="6">
+      <c r="B23" s="4">
         <v>20075</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C23" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D23" s="7">
+      <c r="D23" s="5">
         <v>3002001</v>
       </c>
-      <c r="E23" s="7" t="s">
+      <c r="E23" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="F23" s="8" t="s">
+      <c r="F23" s="6" t="s">
         <v>28</v>
       </c>
       <c r="G23" t="s">
@@ -2561,19 +2522,19 @@
       <c r="A24">
         <v>200020</v>
       </c>
-      <c r="B24" s="6">
+      <c r="B24" s="4">
         <v>20075</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="C24" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D24" s="7">
+      <c r="D24" s="5">
         <v>3002002</v>
       </c>
-      <c r="E24" s="7" t="s">
+      <c r="E24" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="F24" s="9" t="s">
+      <c r="F24" s="7" t="s">
         <v>34</v>
       </c>
       <c r="G24" t="s">
@@ -2605,19 +2566,19 @@
       <c r="A25">
         <v>200021</v>
       </c>
-      <c r="B25" s="6">
+      <c r="B25" s="4">
         <v>20075</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C25" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D25" s="7">
+      <c r="D25" s="5">
         <v>3002003</v>
       </c>
-      <c r="E25" s="7" t="s">
+      <c r="E25" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="F25" s="10" t="s">
+      <c r="F25" s="8" t="s">
         <v>35</v>
       </c>
       <c r="G25" t="s">
@@ -2649,19 +2610,19 @@
       <c r="A26">
         <v>200022</v>
       </c>
-      <c r="B26" s="6">
+      <c r="B26" s="4">
         <v>20050</v>
       </c>
-      <c r="C26" s="6" t="s">
+      <c r="C26" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D26" s="7">
+      <c r="D26" s="5">
         <v>3002001</v>
       </c>
-      <c r="E26" s="7" t="s">
+      <c r="E26" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="F26" s="8" t="s">
+      <c r="F26" s="6" t="s">
         <v>28</v>
       </c>
       <c r="G26" t="s">
@@ -2693,19 +2654,19 @@
       <c r="A27">
         <v>200023</v>
       </c>
-      <c r="B27" s="6">
+      <c r="B27" s="4">
         <v>20050</v>
       </c>
-      <c r="C27" s="6" t="s">
+      <c r="C27" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D27" s="7">
+      <c r="D27" s="5">
         <v>3002002</v>
       </c>
-      <c r="E27" s="7" t="s">
+      <c r="E27" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="F27" s="9" t="s">
+      <c r="F27" s="7" t="s">
         <v>34</v>
       </c>
       <c r="G27" t="s">
@@ -2737,19 +2698,19 @@
       <c r="A28">
         <v>200024</v>
       </c>
-      <c r="B28" s="6">
+      <c r="B28" s="4">
         <v>20050</v>
       </c>
-      <c r="C28" s="6" t="s">
+      <c r="C28" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D28" s="7">
+      <c r="D28" s="5">
         <v>3002003</v>
       </c>
-      <c r="E28" s="7" t="s">
+      <c r="E28" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="F28" s="10" t="s">
+      <c r="F28" s="8" t="s">
         <v>35</v>
       </c>
       <c r="G28" t="s">
@@ -2781,19 +2742,19 @@
       <c r="A29">
         <v>200025</v>
       </c>
-      <c r="B29" s="6">
+      <c r="B29" s="4">
         <v>20025</v>
       </c>
-      <c r="C29" s="6" t="s">
+      <c r="C29" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D29" s="7">
+      <c r="D29" s="5">
         <v>3002001</v>
       </c>
-      <c r="E29" s="7" t="s">
+      <c r="E29" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="F29" s="8" t="s">
+      <c r="F29" s="6" t="s">
         <v>28</v>
       </c>
       <c r="G29" t="s">
@@ -2825,19 +2786,19 @@
       <c r="A30">
         <v>200026</v>
       </c>
-      <c r="B30" s="6">
+      <c r="B30" s="4">
         <v>20025</v>
       </c>
-      <c r="C30" s="6" t="s">
+      <c r="C30" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D30" s="7">
+      <c r="D30" s="5">
         <v>3002002</v>
       </c>
-      <c r="E30" s="7" t="s">
+      <c r="E30" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="F30" s="9" t="s">
+      <c r="F30" s="7" t="s">
         <v>34</v>
       </c>
       <c r="G30" t="s">
@@ -2869,19 +2830,19 @@
       <c r="A31">
         <v>200027</v>
       </c>
-      <c r="B31" s="6">
+      <c r="B31" s="4">
         <v>20025</v>
       </c>
-      <c r="C31" s="6" t="s">
+      <c r="C31" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D31" s="7">
+      <c r="D31" s="5">
         <v>3002003</v>
       </c>
-      <c r="E31" s="7" t="s">
+      <c r="E31" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="F31" s="10" t="s">
+      <c r="F31" s="8" t="s">
         <v>35</v>
       </c>
       <c r="G31" t="s">
@@ -2913,19 +2874,19 @@
       <c r="A32">
         <v>200028</v>
       </c>
-      <c r="B32" s="6">
+      <c r="B32" s="4">
         <v>20001</v>
       </c>
-      <c r="C32" s="6" t="s">
+      <c r="C32" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="D32" s="7">
+      <c r="D32" s="5">
         <v>3002001</v>
       </c>
-      <c r="E32" s="7" t="s">
+      <c r="E32" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="F32" s="8" t="s">
+      <c r="F32" s="6" t="s">
         <v>28</v>
       </c>
       <c r="G32" t="s">
@@ -2957,19 +2918,19 @@
       <c r="A33">
         <v>200029</v>
       </c>
-      <c r="B33" s="6">
+      <c r="B33" s="4">
         <v>20001</v>
       </c>
-      <c r="C33" s="6" t="s">
+      <c r="C33" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="D33" s="7">
+      <c r="D33" s="5">
         <v>3002002</v>
       </c>
-      <c r="E33" s="7" t="s">
+      <c r="E33" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="F33" s="9" t="s">
+      <c r="F33" s="7" t="s">
         <v>34</v>
       </c>
       <c r="G33" t="s">
@@ -3001,19 +2962,19 @@
       <c r="A34">
         <v>200030</v>
       </c>
-      <c r="B34" s="6">
+      <c r="B34" s="4">
         <v>20001</v>
       </c>
-      <c r="C34" s="6" t="s">
+      <c r="C34" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="D34" s="7">
+      <c r="D34" s="5">
         <v>3002003</v>
       </c>
-      <c r="E34" s="7" t="s">
+      <c r="E34" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="F34" s="10" t="s">
+      <c r="F34" s="8" t="s">
         <v>35</v>
       </c>
       <c r="G34" t="s">
@@ -3039,441 +3000,6 @@
       </c>
       <c r="N34">
         <v>4000</v>
-      </c>
-    </row>
-    <row r="35" ht="16.5" spans="1:14">
-      <c r="A35">
-        <v>200031</v>
-      </c>
-      <c r="B35" s="6">
-        <v>20099</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D35">
-        <v>3004001</v>
-      </c>
-      <c r="E35" t="s">
-        <v>58</v>
-      </c>
-      <c r="F35" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="G35" t="s">
-        <v>29</v>
-      </c>
-      <c r="H35" t="s">
-        <v>60</v>
-      </c>
-      <c r="I35" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="36" ht="16.5" spans="1:14">
-      <c r="A36">
-        <v>200032</v>
-      </c>
-      <c r="B36" s="6">
-        <v>20099</v>
-      </c>
-      <c r="C36" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D36">
-        <v>3004002</v>
-      </c>
-      <c r="E36" t="s">
-        <v>58</v>
-      </c>
-      <c r="F36" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="G36" t="s">
-        <v>29</v>
-      </c>
-      <c r="H36" t="s">
-        <v>60</v>
-      </c>
-      <c r="I36" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="37" ht="16.5" spans="1:14">
-      <c r="A37">
-        <v>200033</v>
-      </c>
-      <c r="B37" s="6">
-        <v>20099</v>
-      </c>
-      <c r="C37" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D37">
-        <v>3004003</v>
-      </c>
-      <c r="E37" t="s">
-        <v>58</v>
-      </c>
-      <c r="F37" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="G37" t="s">
-        <v>29</v>
-      </c>
-      <c r="H37" t="s">
-        <v>60</v>
-      </c>
-      <c r="I37" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="38" ht="16.5" spans="1:14">
-      <c r="A38">
-        <v>200034</v>
-      </c>
-      <c r="B38" s="6">
-        <v>20075</v>
-      </c>
-      <c r="C38" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D38">
-        <v>3004001</v>
-      </c>
-      <c r="E38" t="s">
-        <v>58</v>
-      </c>
-      <c r="F38" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="G38" t="s">
-        <v>29</v>
-      </c>
-      <c r="H38" t="s">
-        <v>64</v>
-      </c>
-      <c r="I38" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="39" ht="16.5" spans="1:14">
-      <c r="A39">
-        <v>200035</v>
-      </c>
-      <c r="B39" s="6">
-        <v>20075</v>
-      </c>
-      <c r="C39" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D39">
-        <v>3004002</v>
-      </c>
-      <c r="E39" t="s">
-        <v>58</v>
-      </c>
-      <c r="F39" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="G39" t="s">
-        <v>29</v>
-      </c>
-      <c r="H39" t="s">
-        <v>64</v>
-      </c>
-      <c r="I39" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="40" ht="16.5" spans="1:14">
-      <c r="A40">
-        <v>200036</v>
-      </c>
-      <c r="B40" s="6">
-        <v>20075</v>
-      </c>
-      <c r="C40" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D40">
-        <v>3004003</v>
-      </c>
-      <c r="E40" t="s">
-        <v>58</v>
-      </c>
-      <c r="F40" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="G40" t="s">
-        <v>29</v>
-      </c>
-      <c r="H40" t="s">
-        <v>64</v>
-      </c>
-      <c r="I40" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="41" ht="16.5" spans="1:14">
-      <c r="A41">
-        <v>200037</v>
-      </c>
-      <c r="B41" s="6">
-        <v>20050</v>
-      </c>
-      <c r="C41" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="D41">
-        <v>3004001</v>
-      </c>
-      <c r="E41" t="s">
-        <v>58</v>
-      </c>
-      <c r="F41" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="G41" t="s">
-        <v>43</v>
-      </c>
-      <c r="H41" t="s">
-        <v>66</v>
-      </c>
-      <c r="I41" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="42" ht="16.5" spans="1:14">
-      <c r="A42">
-        <v>200038</v>
-      </c>
-      <c r="B42" s="6">
-        <v>20050</v>
-      </c>
-      <c r="C42" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="D42">
-        <v>3004002</v>
-      </c>
-      <c r="E42" t="s">
-        <v>58</v>
-      </c>
-      <c r="F42" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="G42" t="s">
-        <v>43</v>
-      </c>
-      <c r="H42" t="s">
-        <v>66</v>
-      </c>
-      <c r="I42" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="43" ht="16.5" spans="1:14">
-      <c r="A43">
-        <v>200039</v>
-      </c>
-      <c r="B43" s="6">
-        <v>20050</v>
-      </c>
-      <c r="C43" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="D43">
-        <v>3004003</v>
-      </c>
-      <c r="E43" t="s">
-        <v>58</v>
-      </c>
-      <c r="F43" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="G43" t="s">
-        <v>43</v>
-      </c>
-      <c r="H43" t="s">
-        <v>66</v>
-      </c>
-      <c r="I43" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="44" ht="16.5" spans="1:14">
-      <c r="A44">
-        <v>200040</v>
-      </c>
-      <c r="B44" s="6">
-        <v>20025</v>
-      </c>
-      <c r="C44" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="D44">
-        <v>3004001</v>
-      </c>
-      <c r="E44" t="s">
-        <v>58</v>
-      </c>
-      <c r="F44" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="G44" t="s">
-        <v>43</v>
-      </c>
-      <c r="H44" t="s">
-        <v>68</v>
-      </c>
-      <c r="I44" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="45" ht="16.5" spans="1:14">
-      <c r="A45">
-        <v>200041</v>
-      </c>
-      <c r="B45" s="6">
-        <v>20025</v>
-      </c>
-      <c r="C45" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="D45">
-        <v>3004002</v>
-      </c>
-      <c r="E45" t="s">
-        <v>58</v>
-      </c>
-      <c r="F45" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="G45" t="s">
-        <v>43</v>
-      </c>
-      <c r="H45" t="s">
-        <v>68</v>
-      </c>
-      <c r="I45" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="46" ht="16.5" spans="1:14">
-      <c r="A46">
-        <v>200042</v>
-      </c>
-      <c r="B46" s="6">
-        <v>20025</v>
-      </c>
-      <c r="C46" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="D46">
-        <v>3004003</v>
-      </c>
-      <c r="E46" t="s">
-        <v>58</v>
-      </c>
-      <c r="F46" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="G46" t="s">
-        <v>43</v>
-      </c>
-      <c r="H46" t="s">
-        <v>68</v>
-      </c>
-      <c r="I46" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="47" ht="16.5" spans="1:14">
-      <c r="A47">
-        <v>200043</v>
-      </c>
-      <c r="B47" s="6">
-        <v>20001</v>
-      </c>
-      <c r="C47" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="D47">
-        <v>3004001</v>
-      </c>
-      <c r="E47" t="s">
-        <v>58</v>
-      </c>
-      <c r="F47" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="G47" t="s">
-        <v>43</v>
-      </c>
-      <c r="H47" t="s">
-        <v>61</v>
-      </c>
-      <c r="I47" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="48" ht="16.5" spans="1:14">
-      <c r="A48">
-        <v>200044</v>
-      </c>
-      <c r="B48" s="6">
-        <v>20001</v>
-      </c>
-      <c r="C48" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="D48">
-        <v>3004002</v>
-      </c>
-      <c r="E48" t="s">
-        <v>58</v>
-      </c>
-      <c r="F48" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="G48" t="s">
-        <v>43</v>
-      </c>
-      <c r="H48" t="s">
-        <v>61</v>
-      </c>
-      <c r="I48" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="49" ht="16.5" spans="1:9">
-      <c r="A49">
-        <v>200045</v>
-      </c>
-      <c r="B49" s="6">
-        <v>20001</v>
-      </c>
-      <c r="C49" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="D49">
-        <v>3004003</v>
-      </c>
-      <c r="E49" t="s">
-        <v>58</v>
-      </c>
-      <c r="F49" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="G49" t="s">
-        <v>43</v>
-      </c>
-      <c r="H49" t="s">
-        <v>61</v>
-      </c>
-      <c r="I49" t="s">
-        <v>70</v>
       </c>
     </row>
   </sheetData>

--- a/poker/resources/sample/RobotAction_Chess.xlsx
+++ b/poker/resources/sample/RobotAction_Chess.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="ChessRobot" sheetId="1" r:id="rId1"/>
@@ -150,7 +150,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="71">
   <si>
     <t>序列</t>
   </si>
@@ -324,6 +324,45 @@
   </si>
   <si>
     <t>德州</t>
+  </si>
+  <si>
+    <t>南方前进</t>
+  </si>
+  <si>
+    <t>南方前进基础场</t>
+  </si>
+  <si>
+    <t>10000_10000</t>
+  </si>
+  <si>
+    <t>8000_10000</t>
+  </si>
+  <si>
+    <t>南方前进中级场</t>
+  </si>
+  <si>
+    <t>南方前进高级场</t>
+  </si>
+  <si>
+    <t>9500_10000</t>
+  </si>
+  <si>
+    <t>7500_10000</t>
+  </si>
+  <si>
+    <t>9000_10000</t>
+  </si>
+  <si>
+    <t>7000_10000</t>
+  </si>
+  <si>
+    <t>8500_10000</t>
+  </si>
+  <si>
+    <t>6500_10000</t>
+  </si>
+  <si>
+    <t>6000_10000</t>
   </si>
 </sst>
 </file>
@@ -521,6 +560,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -534,18 +585,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -996,6 +1035,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1008,17 +1049,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1545,7 +1584,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N34"/>
+  <dimension ref="A1:N49"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="3" width="10.875" customWidth="1"/>
@@ -1584,19 +1623,19 @@
       <c r="I1" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="K1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="L1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="M1" s="10" t="s">
+      <c r="M1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="N1" s="10" t="s">
+      <c r="N1" s="3" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1607,18 +1646,18 @@
       <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="2"/>
+      <c r="C2" s="4"/>
       <c r="D2" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="2"/>
+      <c r="F2" s="4"/>
       <c r="G2" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="5" t="s">
         <v>13</v>
       </c>
       <c r="J2" t="s">
@@ -1641,15 +1680,15 @@
       <c r="A3" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2" t="s">
+      <c r="C3" s="4"/>
+      <c r="D3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
       <c r="G3" t="s">
         <v>18</v>
       </c>
@@ -1675,30 +1714,30 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" ht="16.5" spans="2:6">
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
+    <row r="4" ht="16.5" spans="1:14">
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
     </row>
     <row r="5" ht="16.5" spans="1:14">
       <c r="A5">
         <v>200001</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="6">
         <v>20099</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="7">
         <v>3001001</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="8" t="s">
         <v>28</v>
       </c>
       <c r="G5" t="s">
@@ -1730,19 +1769,19 @@
       <c r="A6">
         <v>200002</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6" s="6">
         <v>20099</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="7">
         <v>3001002</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G6" t="s">
@@ -1774,19 +1813,19 @@
       <c r="A7">
         <v>200003</v>
       </c>
-      <c r="B7" s="4">
+      <c r="B7" s="6">
         <v>20099</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="7">
         <v>3001003</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="F7" s="10" t="s">
         <v>35</v>
       </c>
       <c r="G7" t="s">
@@ -1818,19 +1857,19 @@
       <c r="A8">
         <v>200004</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8" s="6">
         <v>20075</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8" s="7">
         <v>3001001</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F8" s="8" t="s">
         <v>28</v>
       </c>
       <c r="G8" t="s">
@@ -1862,19 +1901,19 @@
       <c r="A9">
         <v>200005</v>
       </c>
-      <c r="B9" s="4">
+      <c r="B9" s="6">
         <v>20075</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D9" s="7">
         <v>3001002</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G9" t="s">
@@ -1906,19 +1945,19 @@
       <c r="A10">
         <v>200006</v>
       </c>
-      <c r="B10" s="4">
+      <c r="B10" s="6">
         <v>20075</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="5">
+      <c r="D10" s="7">
         <v>3001003</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="F10" s="10" t="s">
         <v>35</v>
       </c>
       <c r="G10" t="s">
@@ -1950,19 +1989,19 @@
       <c r="A11">
         <v>200007</v>
       </c>
-      <c r="B11" s="4">
+      <c r="B11" s="6">
         <v>20050</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="D11" s="5">
+      <c r="D11" s="7">
         <v>3001001</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="F11" s="6" t="s">
+      <c r="F11" s="8" t="s">
         <v>28</v>
       </c>
       <c r="G11" t="s">
@@ -1994,19 +2033,19 @@
       <c r="A12">
         <v>200008</v>
       </c>
-      <c r="B12" s="4">
+      <c r="B12" s="6">
         <v>20050</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="D12" s="5">
+      <c r="D12" s="7">
         <v>3001002</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E12" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G12" t="s">
@@ -2038,19 +2077,19 @@
       <c r="A13">
         <v>200009</v>
       </c>
-      <c r="B13" s="4">
+      <c r="B13" s="6">
         <v>20050</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="D13" s="5">
+      <c r="D13" s="7">
         <v>3001003</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="E13" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="F13" s="8" t="s">
+      <c r="F13" s="10" t="s">
         <v>35</v>
       </c>
       <c r="G13" t="s">
@@ -2082,19 +2121,19 @@
       <c r="A14">
         <v>200010</v>
       </c>
-      <c r="B14" s="4">
+      <c r="B14" s="6">
         <v>20025</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="D14" s="5">
+      <c r="D14" s="7">
         <v>3001001</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="F14" s="6" t="s">
+      <c r="F14" s="8" t="s">
         <v>28</v>
       </c>
       <c r="G14" t="s">
@@ -2126,19 +2165,19 @@
       <c r="A15">
         <v>200011</v>
       </c>
-      <c r="B15" s="4">
+      <c r="B15" s="6">
         <v>20025</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="D15" s="5">
+      <c r="D15" s="7">
         <v>3001002</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="E15" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="F15" s="7" t="s">
+      <c r="F15" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G15" t="s">
@@ -2170,19 +2209,19 @@
       <c r="A16">
         <v>200012</v>
       </c>
-      <c r="B16" s="4">
+      <c r="B16" s="6">
         <v>20025</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="D16" s="5">
+      <c r="D16" s="7">
         <v>3001003</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="E16" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="F16" s="8" t="s">
+      <c r="F16" s="10" t="s">
         <v>35</v>
       </c>
       <c r="G16" t="s">
@@ -2214,19 +2253,19 @@
       <c r="A17">
         <v>200013</v>
       </c>
-      <c r="B17" s="4">
+      <c r="B17" s="6">
         <v>20001</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="D17" s="5">
+      <c r="D17" s="7">
         <v>3001001</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="E17" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="F17" s="6" t="s">
+      <c r="F17" s="8" t="s">
         <v>28</v>
       </c>
       <c r="G17" t="s">
@@ -2258,19 +2297,19 @@
       <c r="A18">
         <v>200014</v>
       </c>
-      <c r="B18" s="4">
+      <c r="B18" s="6">
         <v>20001</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="D18" s="5">
+      <c r="D18" s="7">
         <v>3001002</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="E18" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="F18" s="7" t="s">
+      <c r="F18" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G18" t="s">
@@ -2302,19 +2341,19 @@
       <c r="A19">
         <v>200015</v>
       </c>
-      <c r="B19" s="4">
+      <c r="B19" s="6">
         <v>20001</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="D19" s="5">
+      <c r="D19" s="7">
         <v>3001003</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="E19" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="F19" s="8" t="s">
+      <c r="F19" s="10" t="s">
         <v>35</v>
       </c>
       <c r="G19" t="s">
@@ -2346,19 +2385,19 @@
       <c r="A20">
         <v>200016</v>
       </c>
-      <c r="B20" s="4">
+      <c r="B20" s="6">
         <v>20099</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D20" s="5">
+      <c r="D20" s="7">
         <v>3002001</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="E20" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="F20" s="6" t="s">
+      <c r="F20" s="8" t="s">
         <v>28</v>
       </c>
       <c r="G20" t="s">
@@ -2390,19 +2429,19 @@
       <c r="A21">
         <v>200017</v>
       </c>
-      <c r="B21" s="4">
+      <c r="B21" s="6">
         <v>20099</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D21" s="5">
+      <c r="D21" s="7">
         <v>3002002</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="E21" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="F21" s="7" t="s">
+      <c r="F21" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G21" t="s">
@@ -2434,19 +2473,19 @@
       <c r="A22">
         <v>200018</v>
       </c>
-      <c r="B22" s="4">
+      <c r="B22" s="6">
         <v>20099</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D22" s="5">
+      <c r="D22" s="7">
         <v>3002003</v>
       </c>
-      <c r="E22" s="5" t="s">
+      <c r="E22" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="F22" s="8" t="s">
+      <c r="F22" s="10" t="s">
         <v>35</v>
       </c>
       <c r="G22" t="s">
@@ -2478,19 +2517,19 @@
       <c r="A23">
         <v>200019</v>
       </c>
-      <c r="B23" s="4">
+      <c r="B23" s="6">
         <v>20075</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C23" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D23" s="5">
+      <c r="D23" s="7">
         <v>3002001</v>
       </c>
-      <c r="E23" s="5" t="s">
+      <c r="E23" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="F23" s="6" t="s">
+      <c r="F23" s="8" t="s">
         <v>28</v>
       </c>
       <c r="G23" t="s">
@@ -2522,19 +2561,19 @@
       <c r="A24">
         <v>200020</v>
       </c>
-      <c r="B24" s="4">
+      <c r="B24" s="6">
         <v>20075</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C24" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D24" s="5">
+      <c r="D24" s="7">
         <v>3002002</v>
       </c>
-      <c r="E24" s="5" t="s">
+      <c r="E24" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="F24" s="7" t="s">
+      <c r="F24" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G24" t="s">
@@ -2566,19 +2605,19 @@
       <c r="A25">
         <v>200021</v>
       </c>
-      <c r="B25" s="4">
+      <c r="B25" s="6">
         <v>20075</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C25" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D25" s="5">
+      <c r="D25" s="7">
         <v>3002003</v>
       </c>
-      <c r="E25" s="5" t="s">
+      <c r="E25" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="F25" s="8" t="s">
+      <c r="F25" s="10" t="s">
         <v>35</v>
       </c>
       <c r="G25" t="s">
@@ -2610,19 +2649,19 @@
       <c r="A26">
         <v>200022</v>
       </c>
-      <c r="B26" s="4">
+      <c r="B26" s="6">
         <v>20050</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C26" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="D26" s="5">
+      <c r="D26" s="7">
         <v>3002001</v>
       </c>
-      <c r="E26" s="5" t="s">
+      <c r="E26" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="F26" s="6" t="s">
+      <c r="F26" s="8" t="s">
         <v>28</v>
       </c>
       <c r="G26" t="s">
@@ -2654,19 +2693,19 @@
       <c r="A27">
         <v>200023</v>
       </c>
-      <c r="B27" s="4">
+      <c r="B27" s="6">
         <v>20050</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="C27" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="D27" s="5">
+      <c r="D27" s="7">
         <v>3002002</v>
       </c>
-      <c r="E27" s="5" t="s">
+      <c r="E27" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="F27" s="7" t="s">
+      <c r="F27" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G27" t="s">
@@ -2698,19 +2737,19 @@
       <c r="A28">
         <v>200024</v>
       </c>
-      <c r="B28" s="4">
+      <c r="B28" s="6">
         <v>20050</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="C28" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="D28" s="5">
+      <c r="D28" s="7">
         <v>3002003</v>
       </c>
-      <c r="E28" s="5" t="s">
+      <c r="E28" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="F28" s="8" t="s">
+      <c r="F28" s="10" t="s">
         <v>35</v>
       </c>
       <c r="G28" t="s">
@@ -2742,19 +2781,19 @@
       <c r="A29">
         <v>200025</v>
       </c>
-      <c r="B29" s="4">
+      <c r="B29" s="6">
         <v>20025</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="C29" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="D29" s="5">
+      <c r="D29" s="7">
         <v>3002001</v>
       </c>
-      <c r="E29" s="5" t="s">
+      <c r="E29" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="F29" s="6" t="s">
+      <c r="F29" s="8" t="s">
         <v>28</v>
       </c>
       <c r="G29" t="s">
@@ -2786,19 +2825,19 @@
       <c r="A30">
         <v>200026</v>
       </c>
-      <c r="B30" s="4">
+      <c r="B30" s="6">
         <v>20025</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="C30" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="D30" s="5">
+      <c r="D30" s="7">
         <v>3002002</v>
       </c>
-      <c r="E30" s="5" t="s">
+      <c r="E30" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="F30" s="7" t="s">
+      <c r="F30" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G30" t="s">
@@ -2830,19 +2869,19 @@
       <c r="A31">
         <v>200027</v>
       </c>
-      <c r="B31" s="4">
+      <c r="B31" s="6">
         <v>20025</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="C31" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="D31" s="5">
+      <c r="D31" s="7">
         <v>3002003</v>
       </c>
-      <c r="E31" s="5" t="s">
+      <c r="E31" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="F31" s="8" t="s">
+      <c r="F31" s="10" t="s">
         <v>35</v>
       </c>
       <c r="G31" t="s">
@@ -2874,19 +2913,19 @@
       <c r="A32">
         <v>200028</v>
       </c>
-      <c r="B32" s="4">
+      <c r="B32" s="6">
         <v>20001</v>
       </c>
-      <c r="C32" s="4" t="s">
+      <c r="C32" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="D32" s="5">
+      <c r="D32" s="7">
         <v>3002001</v>
       </c>
-      <c r="E32" s="5" t="s">
+      <c r="E32" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="F32" s="6" t="s">
+      <c r="F32" s="8" t="s">
         <v>28</v>
       </c>
       <c r="G32" t="s">
@@ -2918,19 +2957,19 @@
       <c r="A33">
         <v>200029</v>
       </c>
-      <c r="B33" s="4">
+      <c r="B33" s="6">
         <v>20001</v>
       </c>
-      <c r="C33" s="4" t="s">
+      <c r="C33" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="D33" s="5">
+      <c r="D33" s="7">
         <v>3002002</v>
       </c>
-      <c r="E33" s="5" t="s">
+      <c r="E33" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="F33" s="7" t="s">
+      <c r="F33" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G33" t="s">
@@ -2962,19 +3001,19 @@
       <c r="A34">
         <v>200030</v>
       </c>
-      <c r="B34" s="4">
+      <c r="B34" s="6">
         <v>20001</v>
       </c>
-      <c r="C34" s="4" t="s">
+      <c r="C34" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="D34" s="5">
+      <c r="D34" s="7">
         <v>3002003</v>
       </c>
-      <c r="E34" s="5" t="s">
+      <c r="E34" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="F34" s="8" t="s">
+      <c r="F34" s="10" t="s">
         <v>35</v>
       </c>
       <c r="G34" t="s">
@@ -3000,6 +3039,441 @@
       </c>
       <c r="N34">
         <v>4000</v>
+      </c>
+    </row>
+    <row r="35" customFormat="1" ht="16.5" spans="1:14">
+      <c r="A35">
+        <v>200031</v>
+      </c>
+      <c r="B35" s="6">
+        <v>20099</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D35">
+        <v>3004001</v>
+      </c>
+      <c r="E35" t="s">
+        <v>58</v>
+      </c>
+      <c r="F35" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="G35" t="s">
+        <v>29</v>
+      </c>
+      <c r="H35" t="s">
+        <v>60</v>
+      </c>
+      <c r="I35" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="36" customFormat="1" ht="16.5" spans="1:14">
+      <c r="A36">
+        <v>200032</v>
+      </c>
+      <c r="B36" s="6">
+        <v>20099</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D36">
+        <v>3004002</v>
+      </c>
+      <c r="E36" t="s">
+        <v>58</v>
+      </c>
+      <c r="F36" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="G36" t="s">
+        <v>29</v>
+      </c>
+      <c r="H36" t="s">
+        <v>60</v>
+      </c>
+      <c r="I36" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="37" customFormat="1" ht="16.5" spans="1:14">
+      <c r="A37">
+        <v>200033</v>
+      </c>
+      <c r="B37" s="6">
+        <v>20099</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D37">
+        <v>3004003</v>
+      </c>
+      <c r="E37" t="s">
+        <v>58</v>
+      </c>
+      <c r="F37" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="G37" t="s">
+        <v>29</v>
+      </c>
+      <c r="H37" t="s">
+        <v>60</v>
+      </c>
+      <c r="I37" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="38" customFormat="1" ht="16.5" spans="1:14">
+      <c r="A38">
+        <v>200034</v>
+      </c>
+      <c r="B38" s="6">
+        <v>20075</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D38">
+        <v>3004001</v>
+      </c>
+      <c r="E38" t="s">
+        <v>58</v>
+      </c>
+      <c r="F38" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="G38" t="s">
+        <v>29</v>
+      </c>
+      <c r="H38" t="s">
+        <v>64</v>
+      </c>
+      <c r="I38" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="39" customFormat="1" ht="16.5" spans="1:14">
+      <c r="A39">
+        <v>200035</v>
+      </c>
+      <c r="B39" s="6">
+        <v>20075</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D39">
+        <v>3004002</v>
+      </c>
+      <c r="E39" t="s">
+        <v>58</v>
+      </c>
+      <c r="F39" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="G39" t="s">
+        <v>29</v>
+      </c>
+      <c r="H39" t="s">
+        <v>64</v>
+      </c>
+      <c r="I39" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="40" customFormat="1" ht="16.5" spans="1:14">
+      <c r="A40">
+        <v>200036</v>
+      </c>
+      <c r="B40" s="6">
+        <v>20075</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D40">
+        <v>3004003</v>
+      </c>
+      <c r="E40" t="s">
+        <v>58</v>
+      </c>
+      <c r="F40" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="G40" t="s">
+        <v>29</v>
+      </c>
+      <c r="H40" t="s">
+        <v>64</v>
+      </c>
+      <c r="I40" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="41" customFormat="1" ht="16.5" spans="1:14">
+      <c r="A41">
+        <v>200037</v>
+      </c>
+      <c r="B41" s="6">
+        <v>20050</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D41">
+        <v>3004001</v>
+      </c>
+      <c r="E41" t="s">
+        <v>58</v>
+      </c>
+      <c r="F41" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="G41" t="s">
+        <v>43</v>
+      </c>
+      <c r="H41" t="s">
+        <v>66</v>
+      </c>
+      <c r="I41" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="42" customFormat="1" ht="16.5" spans="1:14">
+      <c r="A42">
+        <v>200038</v>
+      </c>
+      <c r="B42" s="6">
+        <v>20050</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D42">
+        <v>3004002</v>
+      </c>
+      <c r="E42" t="s">
+        <v>58</v>
+      </c>
+      <c r="F42" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="G42" t="s">
+        <v>43</v>
+      </c>
+      <c r="H42" t="s">
+        <v>66</v>
+      </c>
+      <c r="I42" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="43" customFormat="1" ht="16.5" spans="1:14">
+      <c r="A43">
+        <v>200039</v>
+      </c>
+      <c r="B43" s="6">
+        <v>20050</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D43">
+        <v>3004003</v>
+      </c>
+      <c r="E43" t="s">
+        <v>58</v>
+      </c>
+      <c r="F43" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="G43" t="s">
+        <v>43</v>
+      </c>
+      <c r="H43" t="s">
+        <v>66</v>
+      </c>
+      <c r="I43" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="44" customFormat="1" ht="16.5" spans="1:14">
+      <c r="A44">
+        <v>200040</v>
+      </c>
+      <c r="B44" s="6">
+        <v>20025</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D44">
+        <v>3004001</v>
+      </c>
+      <c r="E44" t="s">
+        <v>58</v>
+      </c>
+      <c r="F44" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="G44" t="s">
+        <v>43</v>
+      </c>
+      <c r="H44" t="s">
+        <v>68</v>
+      </c>
+      <c r="I44" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="45" customFormat="1" ht="16.5" spans="1:14">
+      <c r="A45">
+        <v>200041</v>
+      </c>
+      <c r="B45" s="6">
+        <v>20025</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D45">
+        <v>3004002</v>
+      </c>
+      <c r="E45" t="s">
+        <v>58</v>
+      </c>
+      <c r="F45" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="G45" t="s">
+        <v>43</v>
+      </c>
+      <c r="H45" t="s">
+        <v>68</v>
+      </c>
+      <c r="I45" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="46" customFormat="1" ht="16.5" spans="1:14">
+      <c r="A46">
+        <v>200042</v>
+      </c>
+      <c r="B46" s="6">
+        <v>20025</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D46">
+        <v>3004003</v>
+      </c>
+      <c r="E46" t="s">
+        <v>58</v>
+      </c>
+      <c r="F46" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="G46" t="s">
+        <v>43</v>
+      </c>
+      <c r="H46" t="s">
+        <v>68</v>
+      </c>
+      <c r="I46" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="47" customFormat="1" ht="16.5" spans="1:14">
+      <c r="A47">
+        <v>200043</v>
+      </c>
+      <c r="B47" s="6">
+        <v>20001</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D47">
+        <v>3004001</v>
+      </c>
+      <c r="E47" t="s">
+        <v>58</v>
+      </c>
+      <c r="F47" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="G47" t="s">
+        <v>43</v>
+      </c>
+      <c r="H47" t="s">
+        <v>61</v>
+      </c>
+      <c r="I47" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="48" customFormat="1" ht="16.5" spans="1:14">
+      <c r="A48">
+        <v>200044</v>
+      </c>
+      <c r="B48" s="6">
+        <v>20001</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D48">
+        <v>3004002</v>
+      </c>
+      <c r="E48" t="s">
+        <v>58</v>
+      </c>
+      <c r="F48" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="G48" t="s">
+        <v>43</v>
+      </c>
+      <c r="H48" t="s">
+        <v>61</v>
+      </c>
+      <c r="I48" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="49" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A49">
+        <v>200045</v>
+      </c>
+      <c r="B49" s="6">
+        <v>20001</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D49">
+        <v>3004003</v>
+      </c>
+      <c r="E49" t="s">
+        <v>58</v>
+      </c>
+      <c r="F49" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="G49" t="s">
+        <v>43</v>
+      </c>
+      <c r="H49" t="s">
+        <v>61</v>
+      </c>
+      <c r="I49" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>

--- a/poker/resources/sample/RobotAction_Chess.xlsx
+++ b/poker/resources/sample/RobotAction_Chess.xlsx
@@ -150,7 +150,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="73">
   <si>
     <t>序列</t>
   </si>
@@ -363,6 +363,12 @@
   </si>
   <si>
     <t>6000_10000</t>
+  </si>
+  <si>
+    <t>南方前进-体验场</t>
+  </si>
+  <si>
+    <t>南方前进体验场基础场</t>
   </si>
 </sst>
 </file>
@@ -1584,7 +1590,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N49"/>
+  <dimension ref="A1:N64"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="3" width="10.875" customWidth="1"/>
@@ -3476,6 +3482,441 @@
         <v>70</v>
       </c>
     </row>
+    <row r="50" ht="16.5" spans="1:9">
+      <c r="A50">
+        <v>200046</v>
+      </c>
+      <c r="B50" s="6">
+        <v>20099</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D50">
+        <v>30040231</v>
+      </c>
+      <c r="E50" t="s">
+        <v>71</v>
+      </c>
+      <c r="F50" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="G50" t="s">
+        <v>29</v>
+      </c>
+      <c r="H50" t="s">
+        <v>60</v>
+      </c>
+      <c r="I50" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="51" ht="16.5" spans="1:9">
+      <c r="A51">
+        <v>200047</v>
+      </c>
+      <c r="B51" s="6">
+        <v>20099</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D51">
+        <v>30040232</v>
+      </c>
+      <c r="E51" t="s">
+        <v>71</v>
+      </c>
+      <c r="F51" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="G51" t="s">
+        <v>29</v>
+      </c>
+      <c r="H51" t="s">
+        <v>60</v>
+      </c>
+      <c r="I51" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="52" ht="16.5" spans="1:9">
+      <c r="A52">
+        <v>200048</v>
+      </c>
+      <c r="B52" s="6">
+        <v>20099</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D52">
+        <v>30040233</v>
+      </c>
+      <c r="E52" t="s">
+        <v>71</v>
+      </c>
+      <c r="F52" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="G52" t="s">
+        <v>29</v>
+      </c>
+      <c r="H52" t="s">
+        <v>60</v>
+      </c>
+      <c r="I52" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="53" ht="16.5" spans="1:9">
+      <c r="A53">
+        <v>200049</v>
+      </c>
+      <c r="B53" s="6">
+        <v>20075</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D53">
+        <v>30040231</v>
+      </c>
+      <c r="E53" t="s">
+        <v>71</v>
+      </c>
+      <c r="F53" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="G53" t="s">
+        <v>29</v>
+      </c>
+      <c r="H53" t="s">
+        <v>64</v>
+      </c>
+      <c r="I53" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="54" ht="16.5" spans="1:9">
+      <c r="A54">
+        <v>200050</v>
+      </c>
+      <c r="B54" s="6">
+        <v>20075</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D54">
+        <v>30040232</v>
+      </c>
+      <c r="E54" t="s">
+        <v>71</v>
+      </c>
+      <c r="F54" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="G54" t="s">
+        <v>29</v>
+      </c>
+      <c r="H54" t="s">
+        <v>64</v>
+      </c>
+      <c r="I54" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="55" ht="16.5" spans="1:9">
+      <c r="A55">
+        <v>200051</v>
+      </c>
+      <c r="B55" s="6">
+        <v>20075</v>
+      </c>
+      <c r="C55" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D55">
+        <v>30040233</v>
+      </c>
+      <c r="E55" t="s">
+        <v>71</v>
+      </c>
+      <c r="F55" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="G55" t="s">
+        <v>29</v>
+      </c>
+      <c r="H55" t="s">
+        <v>64</v>
+      </c>
+      <c r="I55" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="56" ht="16.5" spans="1:9">
+      <c r="A56">
+        <v>200052</v>
+      </c>
+      <c r="B56" s="6">
+        <v>20050</v>
+      </c>
+      <c r="C56" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D56">
+        <v>30040231</v>
+      </c>
+      <c r="E56" t="s">
+        <v>71</v>
+      </c>
+      <c r="F56" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="G56" t="s">
+        <v>43</v>
+      </c>
+      <c r="H56" t="s">
+        <v>66</v>
+      </c>
+      <c r="I56" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="57" ht="16.5" spans="1:9">
+      <c r="A57">
+        <v>200053</v>
+      </c>
+      <c r="B57" s="6">
+        <v>20050</v>
+      </c>
+      <c r="C57" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D57">
+        <v>30040232</v>
+      </c>
+      <c r="E57" t="s">
+        <v>71</v>
+      </c>
+      <c r="F57" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="G57" t="s">
+        <v>43</v>
+      </c>
+      <c r="H57" t="s">
+        <v>66</v>
+      </c>
+      <c r="I57" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="58" ht="16.5" spans="1:9">
+      <c r="A58">
+        <v>200054</v>
+      </c>
+      <c r="B58" s="6">
+        <v>20050</v>
+      </c>
+      <c r="C58" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D58">
+        <v>30040233</v>
+      </c>
+      <c r="E58" t="s">
+        <v>71</v>
+      </c>
+      <c r="F58" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="G58" t="s">
+        <v>43</v>
+      </c>
+      <c r="H58" t="s">
+        <v>66</v>
+      </c>
+      <c r="I58" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="59" ht="16.5" spans="1:9">
+      <c r="A59">
+        <v>200055</v>
+      </c>
+      <c r="B59" s="6">
+        <v>20025</v>
+      </c>
+      <c r="C59" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D59">
+        <v>30040231</v>
+      </c>
+      <c r="E59" t="s">
+        <v>71</v>
+      </c>
+      <c r="F59" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="G59" t="s">
+        <v>43</v>
+      </c>
+      <c r="H59" t="s">
+        <v>68</v>
+      </c>
+      <c r="I59" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="60" ht="16.5" spans="1:9">
+      <c r="A60">
+        <v>200056</v>
+      </c>
+      <c r="B60" s="6">
+        <v>20025</v>
+      </c>
+      <c r="C60" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D60">
+        <v>30040232</v>
+      </c>
+      <c r="E60" t="s">
+        <v>71</v>
+      </c>
+      <c r="F60" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="G60" t="s">
+        <v>43</v>
+      </c>
+      <c r="H60" t="s">
+        <v>68</v>
+      </c>
+      <c r="I60" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="61" ht="16.5" spans="1:9">
+      <c r="A61">
+        <v>200057</v>
+      </c>
+      <c r="B61" s="6">
+        <v>20025</v>
+      </c>
+      <c r="C61" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D61">
+        <v>30040233</v>
+      </c>
+      <c r="E61" t="s">
+        <v>71</v>
+      </c>
+      <c r="F61" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="G61" t="s">
+        <v>43</v>
+      </c>
+      <c r="H61" t="s">
+        <v>68</v>
+      </c>
+      <c r="I61" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="62" ht="16.5" spans="1:9">
+      <c r="A62">
+        <v>200058</v>
+      </c>
+      <c r="B62" s="6">
+        <v>20001</v>
+      </c>
+      <c r="C62" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D62">
+        <v>30040231</v>
+      </c>
+      <c r="E62" t="s">
+        <v>71</v>
+      </c>
+      <c r="F62" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="G62" t="s">
+        <v>43</v>
+      </c>
+      <c r="H62" t="s">
+        <v>61</v>
+      </c>
+      <c r="I62" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="63" ht="16.5" spans="1:9">
+      <c r="A63">
+        <v>200059</v>
+      </c>
+      <c r="B63" s="6">
+        <v>20001</v>
+      </c>
+      <c r="C63" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D63">
+        <v>30040232</v>
+      </c>
+      <c r="E63" t="s">
+        <v>71</v>
+      </c>
+      <c r="F63" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="G63" t="s">
+        <v>43</v>
+      </c>
+      <c r="H63" t="s">
+        <v>61</v>
+      </c>
+      <c r="I63" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="64" ht="16.5" spans="1:9">
+      <c r="A64">
+        <v>200060</v>
+      </c>
+      <c r="B64" s="6">
+        <v>20001</v>
+      </c>
+      <c r="C64" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D64">
+        <v>30040233</v>
+      </c>
+      <c r="E64" t="s">
+        <v>71</v>
+      </c>
+      <c r="F64" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="G64" t="s">
+        <v>43</v>
+      </c>
+      <c r="H64" t="s">
+        <v>61</v>
+      </c>
+      <c r="I64" t="s">
+        <v>70</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/poker/resources/sample/RobotAction_Chess.xlsx
+++ b/poker/resources/sample/RobotAction_Chess.xlsx
@@ -150,7 +150,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="73">
   <si>
     <t>序列</t>
   </si>
@@ -363,6 +363,12 @@
   </si>
   <si>
     <t>6000_10000</t>
+  </si>
+  <si>
+    <t>南方前进-体验场</t>
+  </si>
+  <si>
+    <t>南方前进体验场基础场</t>
   </si>
 </sst>
 </file>
@@ -1584,12 +1590,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N49"/>
+  <dimension ref="A1:N64"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="3" width="10.875" customWidth="1"/>
     <col min="4" max="5" width="9.375" customWidth="1"/>
-    <col min="6" max="6" width="11.25" customWidth="1"/>
+    <col min="6" max="6" width="15.2833333333333" customWidth="1"/>
     <col min="7" max="7" width="26.625" customWidth="1"/>
     <col min="8" max="8" width="30.2916666666667" customWidth="1"/>
     <col min="9" max="9" width="31.9083333333333" customWidth="1"/>
@@ -3041,7 +3047,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="35" customFormat="1" ht="16.5" spans="1:14">
+    <row r="35" ht="16.5" spans="1:14">
       <c r="A35">
         <v>200031</v>
       </c>
@@ -3070,7 +3076,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="36" customFormat="1" ht="16.5" spans="1:14">
+    <row r="36" ht="16.5" spans="1:14">
       <c r="A36">
         <v>200032</v>
       </c>
@@ -3099,7 +3105,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="37" customFormat="1" ht="16.5" spans="1:14">
+    <row r="37" ht="16.5" spans="1:14">
       <c r="A37">
         <v>200033</v>
       </c>
@@ -3128,7 +3134,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="38" customFormat="1" ht="16.5" spans="1:14">
+    <row r="38" ht="16.5" spans="1:14">
       <c r="A38">
         <v>200034</v>
       </c>
@@ -3157,7 +3163,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="39" customFormat="1" ht="16.5" spans="1:14">
+    <row r="39" ht="16.5" spans="1:14">
       <c r="A39">
         <v>200035</v>
       </c>
@@ -3186,7 +3192,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="40" customFormat="1" ht="16.5" spans="1:14">
+    <row r="40" ht="16.5" spans="1:14">
       <c r="A40">
         <v>200036</v>
       </c>
@@ -3215,7 +3221,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="41" customFormat="1" ht="16.5" spans="1:14">
+    <row r="41" ht="16.5" spans="1:14">
       <c r="A41">
         <v>200037</v>
       </c>
@@ -3244,7 +3250,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="42" customFormat="1" ht="16.5" spans="1:14">
+    <row r="42" ht="16.5" spans="1:14">
       <c r="A42">
         <v>200038</v>
       </c>
@@ -3273,7 +3279,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="43" customFormat="1" ht="16.5" spans="1:14">
+    <row r="43" ht="16.5" spans="1:14">
       <c r="A43">
         <v>200039</v>
       </c>
@@ -3302,7 +3308,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="44" customFormat="1" ht="16.5" spans="1:14">
+    <row r="44" ht="16.5" spans="1:14">
       <c r="A44">
         <v>200040</v>
       </c>
@@ -3331,7 +3337,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="45" customFormat="1" ht="16.5" spans="1:14">
+    <row r="45" ht="16.5" spans="1:14">
       <c r="A45">
         <v>200041</v>
       </c>
@@ -3360,7 +3366,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="46" customFormat="1" ht="16.5" spans="1:14">
+    <row r="46" ht="16.5" spans="1:14">
       <c r="A46">
         <v>200042</v>
       </c>
@@ -3389,7 +3395,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="47" customFormat="1" ht="16.5" spans="1:14">
+    <row r="47" ht="16.5" spans="1:14">
       <c r="A47">
         <v>200043</v>
       </c>
@@ -3418,7 +3424,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="48" customFormat="1" ht="16.5" spans="1:14">
+    <row r="48" ht="16.5" spans="1:14">
       <c r="A48">
         <v>200044</v>
       </c>
@@ -3447,7 +3453,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="49" customFormat="1" ht="16.5" spans="1:9">
+    <row r="49" ht="16.5" spans="1:9">
       <c r="A49">
         <v>200045</v>
       </c>
@@ -3473,6 +3479,441 @@
         <v>61</v>
       </c>
       <c r="I49" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="50" ht="16.5" spans="1:9">
+      <c r="A50">
+        <v>200046</v>
+      </c>
+      <c r="B50" s="6">
+        <v>20099</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D50">
+        <v>30040231</v>
+      </c>
+      <c r="E50" t="s">
+        <v>71</v>
+      </c>
+      <c r="F50" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="G50" t="s">
+        <v>29</v>
+      </c>
+      <c r="H50" t="s">
+        <v>60</v>
+      </c>
+      <c r="I50" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="51" ht="16.5" spans="1:9">
+      <c r="A51">
+        <v>200047</v>
+      </c>
+      <c r="B51" s="6">
+        <v>20099</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D51">
+        <v>30040232</v>
+      </c>
+      <c r="E51" t="s">
+        <v>71</v>
+      </c>
+      <c r="F51" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="G51" t="s">
+        <v>29</v>
+      </c>
+      <c r="H51" t="s">
+        <v>60</v>
+      </c>
+      <c r="I51" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="52" ht="16.5" spans="1:9">
+      <c r="A52">
+        <v>200048</v>
+      </c>
+      <c r="B52" s="6">
+        <v>20099</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D52">
+        <v>30040233</v>
+      </c>
+      <c r="E52" t="s">
+        <v>71</v>
+      </c>
+      <c r="F52" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="G52" t="s">
+        <v>29</v>
+      </c>
+      <c r="H52" t="s">
+        <v>60</v>
+      </c>
+      <c r="I52" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="53" ht="16.5" spans="1:9">
+      <c r="A53">
+        <v>200049</v>
+      </c>
+      <c r="B53" s="6">
+        <v>20075</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D53">
+        <v>30040231</v>
+      </c>
+      <c r="E53" t="s">
+        <v>71</v>
+      </c>
+      <c r="F53" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="G53" t="s">
+        <v>29</v>
+      </c>
+      <c r="H53" t="s">
+        <v>64</v>
+      </c>
+      <c r="I53" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="54" ht="16.5" spans="1:9">
+      <c r="A54">
+        <v>200050</v>
+      </c>
+      <c r="B54" s="6">
+        <v>20075</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D54">
+        <v>30040232</v>
+      </c>
+      <c r="E54" t="s">
+        <v>71</v>
+      </c>
+      <c r="F54" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="G54" t="s">
+        <v>29</v>
+      </c>
+      <c r="H54" t="s">
+        <v>64</v>
+      </c>
+      <c r="I54" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="55" ht="16.5" spans="1:9">
+      <c r="A55">
+        <v>200051</v>
+      </c>
+      <c r="B55" s="6">
+        <v>20075</v>
+      </c>
+      <c r="C55" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D55">
+        <v>30040233</v>
+      </c>
+      <c r="E55" t="s">
+        <v>71</v>
+      </c>
+      <c r="F55" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="G55" t="s">
+        <v>29</v>
+      </c>
+      <c r="H55" t="s">
+        <v>64</v>
+      </c>
+      <c r="I55" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="56" ht="16.5" spans="1:9">
+      <c r="A56">
+        <v>200052</v>
+      </c>
+      <c r="B56" s="6">
+        <v>20050</v>
+      </c>
+      <c r="C56" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D56">
+        <v>30040231</v>
+      </c>
+      <c r="E56" t="s">
+        <v>71</v>
+      </c>
+      <c r="F56" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="G56" t="s">
+        <v>43</v>
+      </c>
+      <c r="H56" t="s">
+        <v>66</v>
+      </c>
+      <c r="I56" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="57" ht="16.5" spans="1:9">
+      <c r="A57">
+        <v>200053</v>
+      </c>
+      <c r="B57" s="6">
+        <v>20050</v>
+      </c>
+      <c r="C57" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D57">
+        <v>30040232</v>
+      </c>
+      <c r="E57" t="s">
+        <v>71</v>
+      </c>
+      <c r="F57" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="G57" t="s">
+        <v>43</v>
+      </c>
+      <c r="H57" t="s">
+        <v>66</v>
+      </c>
+      <c r="I57" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="58" ht="16.5" spans="1:9">
+      <c r="A58">
+        <v>200054</v>
+      </c>
+      <c r="B58" s="6">
+        <v>20050</v>
+      </c>
+      <c r="C58" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D58">
+        <v>30040233</v>
+      </c>
+      <c r="E58" t="s">
+        <v>71</v>
+      </c>
+      <c r="F58" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="G58" t="s">
+        <v>43</v>
+      </c>
+      <c r="H58" t="s">
+        <v>66</v>
+      </c>
+      <c r="I58" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="59" ht="16.5" spans="1:9">
+      <c r="A59">
+        <v>200055</v>
+      </c>
+      <c r="B59" s="6">
+        <v>20025</v>
+      </c>
+      <c r="C59" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D59">
+        <v>30040231</v>
+      </c>
+      <c r="E59" t="s">
+        <v>71</v>
+      </c>
+      <c r="F59" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="G59" t="s">
+        <v>43</v>
+      </c>
+      <c r="H59" t="s">
+        <v>68</v>
+      </c>
+      <c r="I59" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="60" ht="16.5" spans="1:9">
+      <c r="A60">
+        <v>200056</v>
+      </c>
+      <c r="B60" s="6">
+        <v>20025</v>
+      </c>
+      <c r="C60" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D60">
+        <v>30040232</v>
+      </c>
+      <c r="E60" t="s">
+        <v>71</v>
+      </c>
+      <c r="F60" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="G60" t="s">
+        <v>43</v>
+      </c>
+      <c r="H60" t="s">
+        <v>68</v>
+      </c>
+      <c r="I60" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="61" ht="16.5" spans="1:9">
+      <c r="A61">
+        <v>200057</v>
+      </c>
+      <c r="B61" s="6">
+        <v>20025</v>
+      </c>
+      <c r="C61" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D61">
+        <v>30040233</v>
+      </c>
+      <c r="E61" t="s">
+        <v>71</v>
+      </c>
+      <c r="F61" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="G61" t="s">
+        <v>43</v>
+      </c>
+      <c r="H61" t="s">
+        <v>68</v>
+      </c>
+      <c r="I61" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="62" ht="16.5" spans="1:9">
+      <c r="A62">
+        <v>200058</v>
+      </c>
+      <c r="B62" s="6">
+        <v>20001</v>
+      </c>
+      <c r="C62" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D62">
+        <v>30040231</v>
+      </c>
+      <c r="E62" t="s">
+        <v>71</v>
+      </c>
+      <c r="F62" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="G62" t="s">
+        <v>43</v>
+      </c>
+      <c r="H62" t="s">
+        <v>61</v>
+      </c>
+      <c r="I62" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="63" ht="16.5" spans="1:9">
+      <c r="A63">
+        <v>200059</v>
+      </c>
+      <c r="B63" s="6">
+        <v>20001</v>
+      </c>
+      <c r="C63" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D63">
+        <v>30040232</v>
+      </c>
+      <c r="E63" t="s">
+        <v>71</v>
+      </c>
+      <c r="F63" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="G63" t="s">
+        <v>43</v>
+      </c>
+      <c r="H63" t="s">
+        <v>61</v>
+      </c>
+      <c r="I63" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="64" ht="16.5" spans="1:9">
+      <c r="A64">
+        <v>200060</v>
+      </c>
+      <c r="B64" s="6">
+        <v>20001</v>
+      </c>
+      <c r="C64" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D64">
+        <v>30040233</v>
+      </c>
+      <c r="E64" t="s">
+        <v>71</v>
+      </c>
+      <c r="F64" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="G64" t="s">
+        <v>43</v>
+      </c>
+      <c r="H64" t="s">
+        <v>61</v>
+      </c>
+      <c r="I64" t="s">
         <v>70</v>
       </c>
     </row>

--- a/poker/resources/sample/RobotAction_Chess.xlsx
+++ b/poker/resources/sample/RobotAction_Chess.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="ChessRobot" sheetId="1" r:id="rId1"/>
@@ -150,7 +150,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="78">
   <si>
     <t>序列</t>
   </si>
@@ -369,6 +369,21 @@
   </si>
   <si>
     <t>南方前进体验场基础场</t>
+  </si>
+  <si>
+    <t>斗仙牌</t>
+  </si>
+  <si>
+    <t>斗仙牌基础场</t>
+  </si>
+  <si>
+    <t>70,4000,8000|30,2000,4000</t>
+  </si>
+  <si>
+    <t>斗仙牌中级场</t>
+  </si>
+  <si>
+    <t>斗仙牌高级场</t>
   </si>
 </sst>
 </file>
@@ -1590,7 +1605,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N64"/>
+  <dimension ref="A1:N79"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="3" width="10.875" customWidth="1"/>
@@ -3917,6 +3932,441 @@
         <v>70</v>
       </c>
     </row>
+    <row r="65" ht="16.5" spans="1:9">
+      <c r="A65">
+        <v>200061</v>
+      </c>
+      <c r="B65" s="6">
+        <v>20099</v>
+      </c>
+      <c r="C65" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D65">
+        <v>3008001</v>
+      </c>
+      <c r="E65" t="s">
+        <v>73</v>
+      </c>
+      <c r="F65" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="G65" t="s">
+        <v>75</v>
+      </c>
+      <c r="H65" t="s">
+        <v>30</v>
+      </c>
+      <c r="I65" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="66" ht="16.5" spans="1:9">
+      <c r="A66">
+        <v>200062</v>
+      </c>
+      <c r="B66" s="6">
+        <v>20099</v>
+      </c>
+      <c r="C66" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D66">
+        <v>3008002</v>
+      </c>
+      <c r="E66" t="s">
+        <v>73</v>
+      </c>
+      <c r="F66" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="G66" t="s">
+        <v>75</v>
+      </c>
+      <c r="H66" t="s">
+        <v>30</v>
+      </c>
+      <c r="I66" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="67" ht="16.5" spans="1:9">
+      <c r="A67">
+        <v>200063</v>
+      </c>
+      <c r="B67" s="6">
+        <v>20099</v>
+      </c>
+      <c r="C67" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D67">
+        <v>3008003</v>
+      </c>
+      <c r="E67" t="s">
+        <v>73</v>
+      </c>
+      <c r="F67" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G67" t="s">
+        <v>75</v>
+      </c>
+      <c r="H67" t="s">
+        <v>30</v>
+      </c>
+      <c r="I67" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="68" ht="16.5" spans="1:9">
+      <c r="A68">
+        <v>200064</v>
+      </c>
+      <c r="B68" s="6">
+        <v>20075</v>
+      </c>
+      <c r="C68" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D68">
+        <v>3008001</v>
+      </c>
+      <c r="E68" t="s">
+        <v>73</v>
+      </c>
+      <c r="F68" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="G68" t="s">
+        <v>75</v>
+      </c>
+      <c r="H68" t="s">
+        <v>37</v>
+      </c>
+      <c r="I68" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="69" ht="16.5" spans="1:9">
+      <c r="A69">
+        <v>200065</v>
+      </c>
+      <c r="B69" s="6">
+        <v>20075</v>
+      </c>
+      <c r="C69" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D69">
+        <v>3008002</v>
+      </c>
+      <c r="E69" t="s">
+        <v>73</v>
+      </c>
+      <c r="F69" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="G69" t="s">
+        <v>75</v>
+      </c>
+      <c r="H69" t="s">
+        <v>37</v>
+      </c>
+      <c r="I69" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="70" ht="16.5" spans="1:9">
+      <c r="A70">
+        <v>200066</v>
+      </c>
+      <c r="B70" s="6">
+        <v>20075</v>
+      </c>
+      <c r="C70" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D70">
+        <v>3008003</v>
+      </c>
+      <c r="E70" t="s">
+        <v>73</v>
+      </c>
+      <c r="F70" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G70" t="s">
+        <v>75</v>
+      </c>
+      <c r="H70" t="s">
+        <v>37</v>
+      </c>
+      <c r="I70" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="71" ht="16.5" spans="1:9">
+      <c r="A71">
+        <v>200067</v>
+      </c>
+      <c r="B71" s="6">
+        <v>20050</v>
+      </c>
+      <c r="C71" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D71">
+        <v>3008001</v>
+      </c>
+      <c r="E71" t="s">
+        <v>73</v>
+      </c>
+      <c r="F71" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="G71" t="s">
+        <v>75</v>
+      </c>
+      <c r="H71" t="s">
+        <v>44</v>
+      </c>
+      <c r="I71" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="72" ht="16.5" spans="1:9">
+      <c r="A72">
+        <v>200068</v>
+      </c>
+      <c r="B72" s="6">
+        <v>20050</v>
+      </c>
+      <c r="C72" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D72">
+        <v>3008002</v>
+      </c>
+      <c r="E72" t="s">
+        <v>73</v>
+      </c>
+      <c r="F72" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="G72" t="s">
+        <v>75</v>
+      </c>
+      <c r="H72" t="s">
+        <v>44</v>
+      </c>
+      <c r="I72" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="73" ht="16.5" spans="1:9">
+      <c r="A73">
+        <v>200069</v>
+      </c>
+      <c r="B73" s="6">
+        <v>20050</v>
+      </c>
+      <c r="C73" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D73">
+        <v>3008003</v>
+      </c>
+      <c r="E73" t="s">
+        <v>73</v>
+      </c>
+      <c r="F73" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G73" t="s">
+        <v>75</v>
+      </c>
+      <c r="H73" t="s">
+        <v>44</v>
+      </c>
+      <c r="I73" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="74" ht="16.5" spans="1:9">
+      <c r="A74">
+        <v>200070</v>
+      </c>
+      <c r="B74" s="6">
+        <v>20025</v>
+      </c>
+      <c r="C74" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D74">
+        <v>3008001</v>
+      </c>
+      <c r="E74" t="s">
+        <v>73</v>
+      </c>
+      <c r="F74" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="G74" t="s">
+        <v>75</v>
+      </c>
+      <c r="H74" t="s">
+        <v>49</v>
+      </c>
+      <c r="I74" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="75" ht="16.5" spans="1:9">
+      <c r="A75">
+        <v>200071</v>
+      </c>
+      <c r="B75" s="6">
+        <v>20025</v>
+      </c>
+      <c r="C75" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D75">
+        <v>3008002</v>
+      </c>
+      <c r="E75" t="s">
+        <v>73</v>
+      </c>
+      <c r="F75" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="G75" t="s">
+        <v>75</v>
+      </c>
+      <c r="H75" t="s">
+        <v>49</v>
+      </c>
+      <c r="I75" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="76" ht="16.5" spans="1:9">
+      <c r="A76">
+        <v>200072</v>
+      </c>
+      <c r="B76" s="6">
+        <v>20025</v>
+      </c>
+      <c r="C76" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D76">
+        <v>3008003</v>
+      </c>
+      <c r="E76" t="s">
+        <v>73</v>
+      </c>
+      <c r="F76" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G76" t="s">
+        <v>75</v>
+      </c>
+      <c r="H76" t="s">
+        <v>49</v>
+      </c>
+      <c r="I76" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="77" ht="16.5" spans="1:9">
+      <c r="A77">
+        <v>200073</v>
+      </c>
+      <c r="B77" s="6">
+        <v>20001</v>
+      </c>
+      <c r="C77" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D77">
+        <v>3008001</v>
+      </c>
+      <c r="E77" t="s">
+        <v>73</v>
+      </c>
+      <c r="F77" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="G77" t="s">
+        <v>75</v>
+      </c>
+      <c r="H77" t="s">
+        <v>54</v>
+      </c>
+      <c r="I77" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="78" ht="16.5" spans="1:9">
+      <c r="A78">
+        <v>200074</v>
+      </c>
+      <c r="B78" s="6">
+        <v>20001</v>
+      </c>
+      <c r="C78" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D78">
+        <v>3008002</v>
+      </c>
+      <c r="E78" t="s">
+        <v>73</v>
+      </c>
+      <c r="F78" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="G78" t="s">
+        <v>75</v>
+      </c>
+      <c r="H78" t="s">
+        <v>54</v>
+      </c>
+      <c r="I78" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="79" ht="16.5" spans="1:9">
+      <c r="A79">
+        <v>200075</v>
+      </c>
+      <c r="B79" s="6">
+        <v>20001</v>
+      </c>
+      <c r="C79" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D79">
+        <v>3008003</v>
+      </c>
+      <c r="E79" t="s">
+        <v>73</v>
+      </c>
+      <c r="F79" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G79" t="s">
+        <v>75</v>
+      </c>
+      <c r="H79" t="s">
+        <v>54</v>
+      </c>
+      <c r="I79" t="s">
+        <v>55</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
